--- a/jira_export_2026-09-02.xlsx
+++ b/jira_export_2026-09-02.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>27 h</t>
+          <t>34 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P64"/>
+  <dimension ref="A1:P68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -942,7 +942,7 @@
     <col width="46" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
@@ -1190,27 +1190,27 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34975</t>
+          <t>PDMDEP-35029</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE SURESNES] - Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
+          <t>[VILLE DE LEVALLOIS PERRET] - Hébergement Litt Exp test et prod</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE SURESNES</t>
+          <t>VILLE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
+          <t xml:space="preserve">Hébergement Litt Exp </t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H7" s="11" t="inlineStr">
@@ -1230,29 +1230,21 @@
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="J7" s="11" t="n">
         <v>1</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-34979</t>
-        </is>
-      </c>
-      <c r="M7" s="11" t="inlineStr">
-        <is>
-          <t>00178226</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L7" s="11" t="inlineStr"/>
+      <c r="M7" s="11" t="inlineStr"/>
       <c r="N7" s="12" t="n">
-        <v>1100</v>
-      </c>
-      <c r="O7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P7" s="12" t="n">
@@ -1262,32 +1254,32 @@
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34819</t>
+          <t>PDMDEP-34975</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>[Ville de Bourges] - Migration GEODP Placier et ODP</t>
+          <t>[VILLE DE SURESNES] - Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>Ville de Bourges</t>
+          <t>VILLE DE SURESNES</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier et ODP</t>
+          <t>Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -1297,32 +1289,32 @@
       </c>
       <c r="H8" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I8" s="14" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="J8" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K8" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34825</t>
+          <t>PDMDEP-34979</t>
         </is>
       </c>
       <c r="M8" s="14" t="inlineStr">
         <is>
-          <t>00177218</t>
+          <t>00178226</t>
         </is>
       </c>
       <c r="N8" s="15" t="n">
-        <v>2419</v>
+        <v>1100</v>
       </c>
       <c r="O8" s="16" t="n">
         <v>0</v>
@@ -1334,32 +1326,32 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34718</t>
+          <t>PDMDEP-34819</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE VILLEURBANNE] - Crédits d'heure (14h)</t>
+          <t>[Ville de Bourges] - Migration GEODP Placier et ODP</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEURBANNE</t>
+          <t>Ville de Bourges</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Crédits d'heure (14h)</t>
+          <t>Migration GEODP Placier et ODP</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
@@ -1369,32 +1361,32 @@
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="J9" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34722</t>
+          <t>PDMDEP-34825</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
-          <t>00176875</t>
+          <t>00177218</t>
         </is>
       </c>
       <c r="N9" s="12" t="n">
-        <v>1260</v>
+        <v>2419</v>
       </c>
       <c r="O9" s="16" t="n">
         <v>0</v>
@@ -1406,32 +1398,32 @@
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34411</t>
+          <t>PDMDEP-34718</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE MAIZIERES LES METZ] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[VILLE DE VILLEURBANNE] - Crédits d'heure (14h)</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE MAIZIERES LES METZ</t>
+          <t>VILLE DE VILLEURBANNE</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>Crédits d'heure (14h)</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -1441,34 +1433,34 @@
       </c>
       <c r="H10" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="J10" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K10" s="14" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L10" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34420</t>
+          <t>PDMDEP-34722</t>
         </is>
       </c>
       <c r="M10" s="14" t="inlineStr">
         <is>
-          <t>00172317</t>
+          <t>00176875</t>
         </is>
       </c>
       <c r="N10" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="15" t="n">
+        <v>1260</v>
+      </c>
+      <c r="O10" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P10" s="15" t="n">
@@ -1478,12 +1470,12 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34319</t>
+          <t>PDMDEP-34411</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
+          <t>[MAIRIE DE MAIZIERES LES METZ] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
@@ -1493,12 +1485,12 @@
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Commune de Mouscron (BE)</t>
+          <t>MAIRIE DE MAIZIERES LES METZ</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
@@ -1518,29 +1510,29 @@
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="J11" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34326</t>
+          <t>PDMDEP-34420</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
         <is>
-          <t>00171691</t>
+          <t>00172317</t>
         </is>
       </c>
       <c r="N11" s="12" t="n">
-        <v>769.5</v>
-      </c>
-      <c r="O11" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P11" s="12" t="n">
@@ -1550,27 +1542,27 @@
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34249</t>
+          <t>PDMDEP-34319</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
+          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIENNE</t>
+          <t>Commune de Mouscron (BE)</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration Placier et ODP </t>
+          <t>Migration GEODP Placier</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
@@ -1590,7 +1582,7 @@
       </c>
       <c r="I12" s="14" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="J12" s="14" t="n">
@@ -1601,16 +1593,16 @@
       </c>
       <c r="L12" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34258</t>
+          <t>PDMDEP-34326</t>
         </is>
       </c>
       <c r="M12" s="14" t="inlineStr">
         <is>
-          <t>00171361</t>
+          <t>00171691</t>
         </is>
       </c>
       <c r="N12" s="15" t="n">
-        <v>2127.2</v>
+        <v>769.5</v>
       </c>
       <c r="O12" s="16" t="n">
         <v>0</v>
@@ -1622,32 +1614,32 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34229</t>
+          <t>PDMDEP-34249</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
+          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>COMMUNE DE VIENNE</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>GRC + Connecteur</t>
+          <t xml:space="preserve">Migration Placier et ODP </t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
@@ -1657,12 +1649,12 @@
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J13" s="11" t="n">
@@ -1673,16 +1665,16 @@
       </c>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34235</t>
+          <t>PDMDEP-34258</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
         <is>
-          <t>00171333</t>
+          <t>00171361</t>
         </is>
       </c>
       <c r="N13" s="12" t="n">
-        <v>4536</v>
+        <v>2127.2</v>
       </c>
       <c r="O13" s="16" t="n">
         <v>0</v>
@@ -1694,32 +1686,32 @@
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34208</t>
+          <t>PDMDEP-34229</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
+          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHATEAUGIRON</t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2</t>
+          <t>GRC + Connecteur</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -1729,32 +1721,32 @@
       </c>
       <c r="H14" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="J14" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K14" s="14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34216</t>
+          <t>PDMDEP-34235</t>
         </is>
       </c>
       <c r="M14" s="14" t="inlineStr">
         <is>
-          <t>00171155</t>
+          <t>00171333</t>
         </is>
       </c>
       <c r="N14" s="15" t="n">
-        <v>525</v>
+        <v>4536</v>
       </c>
       <c r="O14" s="16" t="n">
         <v>0</v>
@@ -1766,12 +1758,12 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34192</t>
+          <t>PDMDEP-34208</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Macon ] - GEODP Placier</t>
+          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
@@ -1781,12 +1773,12 @@
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Macon </t>
+          <t>COMMUNE DE CHATEAUGIRON</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>GEODP Placier</t>
+          <t>Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
@@ -1801,7 +1793,7 @@
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I15" s="11" t="inlineStr">
@@ -1817,16 +1809,16 @@
       </c>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34201</t>
+          <t>PDMDEP-34216</t>
         </is>
       </c>
       <c r="M15" s="11" t="inlineStr">
         <is>
-          <t>00171162</t>
+          <t>00171155</t>
         </is>
       </c>
       <c r="N15" s="12" t="n">
-        <v>1662</v>
+        <v>525</v>
       </c>
       <c r="O15" s="16" t="n">
         <v>0</v>
@@ -1838,27 +1830,27 @@
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34169</t>
+          <t>PDMDEP-34192</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[Commune de Macon ] - GEODP Placier</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+          <t xml:space="preserve">Commune de Macon </t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>GEODP Placier</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
@@ -1873,32 +1865,32 @@
       </c>
       <c r="H16" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I16" s="14" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="J16" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K16" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34227</t>
+          <t>PDMDEP-34201</t>
         </is>
       </c>
       <c r="M16" s="14" t="inlineStr">
         <is>
-          <t>2026-0210095</t>
+          <t>00171162</t>
         </is>
       </c>
       <c r="N16" s="15" t="n">
-        <v>9623.1</v>
+        <v>1662</v>
       </c>
       <c r="O16" s="16" t="n">
         <v>0</v>
@@ -1910,12 +1902,12 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34108</t>
+          <t>PDMDEP-34169</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
+          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
@@ -1925,12 +1917,12 @@
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DU PUY EN VELAY</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + migration ODP</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
@@ -1950,7 +1942,7 @@
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="J17" s="11" t="n">
@@ -1961,16 +1953,16 @@
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34117</t>
+          <t>PDMDEP-34227</t>
         </is>
       </c>
       <c r="M17" s="11" t="inlineStr">
         <is>
-          <t>00170907</t>
+          <t>2026-0210095</t>
         </is>
       </c>
       <c r="N17" s="12" t="n">
-        <v>707</v>
+        <v>9623.1</v>
       </c>
       <c r="O17" s="16" t="n">
         <v>0</v>
@@ -1982,12 +1974,12 @@
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34064</t>
+          <t>PDMDEP-34108</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
+          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
@@ -1997,12 +1989,12 @@
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE VANNES</t>
+          <t>COMMUNE DU PUY EN VELAY</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
+          <t>Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
@@ -2017,12 +2009,12 @@
       </c>
       <c r="H18" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="J18" s="14" t="n">
@@ -2033,16 +2025,16 @@
       </c>
       <c r="L18" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34070</t>
+          <t>PDMDEP-34117</t>
         </is>
       </c>
       <c r="M18" s="14" t="inlineStr">
         <is>
-          <t>00170468</t>
+          <t>00170907</t>
         </is>
       </c>
       <c r="N18" s="15" t="n">
-        <v>300</v>
+        <v>707</v>
       </c>
       <c r="O18" s="16" t="n">
         <v>0</v>
@@ -2054,27 +2046,27 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33985</t>
+          <t>PDMDEP-34064</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE QUIMPERLE</t>
+          <t>VILLE DE VANNES</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
@@ -2089,12 +2081,12 @@
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="J19" s="11" t="n">
@@ -2105,16 +2097,16 @@
       </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33991</t>
+          <t>PDMDEP-34070</t>
         </is>
       </c>
       <c r="M19" s="11" t="inlineStr">
         <is>
-          <t>00170408</t>
+          <t>00170468</t>
         </is>
       </c>
       <c r="N19" s="12" t="n">
-        <v>510</v>
+        <v>300</v>
       </c>
       <c r="O19" s="16" t="n">
         <v>0</v>
@@ -2126,32 +2118,32 @@
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33949</t>
+          <t>PDMDEP-33985</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
+          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>Commune de Colmar</t>
+          <t>COMMUNE DE QUIMPERLE</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>Modélisation Littéralis Expert</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
@@ -2161,32 +2153,32 @@
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I20" s="14" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="J20" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K20" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33955</t>
+          <t>PDMDEP-33991</t>
         </is>
       </c>
       <c r="M20" s="14" t="inlineStr">
         <is>
-          <t>00170302</t>
+          <t>00170408</t>
         </is>
       </c>
       <c r="N20" s="15" t="n">
-        <v>242.9</v>
+        <v>510</v>
       </c>
       <c r="O20" s="16" t="n">
         <v>0</v>
@@ -2198,27 +2190,27 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33940</t>
+          <t>PDMDEP-33949</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Thionville] - AME </t>
+          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>Commune de Thionville</t>
+          <t>Commune de Colmar</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>AME Littéralis Expert</t>
+          <t>Modélisation Littéralis Expert</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
@@ -2245,20 +2237,20 @@
         <v>3</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33944</t>
+          <t>PDMDEP-33955</t>
         </is>
       </c>
       <c r="M21" s="11" t="inlineStr">
         <is>
-          <t>00170299</t>
+          <t>00170302</t>
         </is>
       </c>
       <c r="N21" s="12" t="n">
-        <v>220</v>
+        <v>242.9</v>
       </c>
       <c r="O21" s="16" t="n">
         <v>0</v>
@@ -2270,12 +2262,12 @@
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33813</t>
+          <t>PDMDEP-33940</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
+          <t xml:space="preserve">[Commune de Thionville] - AME </t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
@@ -2285,12 +2277,12 @@
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>Commune de Thionville</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>Modélisation Seyne S/ Mer</t>
+          <t>AME Littéralis Expert</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
@@ -2310,29 +2302,29 @@
       </c>
       <c r="I22" s="14" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J22" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K22" s="14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33817</t>
+          <t>PDMDEP-33944</t>
         </is>
       </c>
       <c r="M22" s="14" t="inlineStr">
         <is>
-          <t>00169865</t>
+          <t>00170299</t>
         </is>
       </c>
       <c r="N22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" s="15" t="n">
+        <v>220</v>
+      </c>
+      <c r="O22" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P22" s="15" t="n">
@@ -2342,12 +2334,12 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33804</t>
+          <t>PDMDEP-33813</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>[CD 73)] - Purge arrêtés temporaires</t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
@@ -2357,12 +2349,12 @@
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>Purge arrêtés temporaires</t>
+          <t>Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
@@ -2389,22 +2381,22 @@
         <v>3</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L23" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33808</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="M23" s="11" t="inlineStr">
         <is>
-          <t>00169856</t>
+          <t>00169865</t>
         </is>
       </c>
       <c r="N23" s="12" t="n">
-        <v>1890</v>
-      </c>
-      <c r="O23" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P23" s="12" t="n">
@@ -2414,27 +2406,27 @@
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33739</t>
+          <t>PDMDEP-33804</t>
         </is>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
+          <t>[CD 73)] - Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>UPSELL PASTELL + DA DPA</t>
+          <t>Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
@@ -2454,27 +2446,27 @@
       </c>
       <c r="I24" s="14" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J24" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K24" s="14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33745</t>
+          <t>PDMDEP-33808</t>
         </is>
       </c>
       <c r="M24" s="14" t="inlineStr">
         <is>
-          <t>00169509</t>
+          <t>00169856</t>
         </is>
       </c>
       <c r="N24" s="15" t="n">
-        <v>920</v>
+        <v>1890</v>
       </c>
       <c r="O24" s="16" t="n">
         <v>0</v>
@@ -2486,27 +2478,27 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33471</t>
+          <t>PDMDEP-33739</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
+          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D AUCH</t>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>FDS Facture LiS</t>
+          <t>UPSELL PASTELL + DA DPA</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
@@ -2526,27 +2518,27 @@
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J25" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33475</t>
+          <t>PDMDEP-33745</t>
         </is>
       </c>
       <c r="M25" s="11" t="inlineStr">
         <is>
-          <t>00168025</t>
+          <t>00169509</t>
         </is>
       </c>
       <c r="N25" s="12" t="n">
-        <v>171.4</v>
+        <v>920</v>
       </c>
       <c r="O25" s="16" t="n">
         <v>0</v>
@@ -2558,32 +2550,32 @@
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33395</t>
+          <t>PDMDEP-33471</t>
         </is>
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBELIARD</t>
+          <t>COMMUNE D AUCH</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t>FDS Facture LiS</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G26" s="14" t="inlineStr">
@@ -2598,7 +2590,7 @@
       </c>
       <c r="I26" s="14" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J26" s="14" t="n">
@@ -2609,16 +2601,16 @@
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33401</t>
+          <t>PDMDEP-33475</t>
         </is>
       </c>
       <c r="M26" s="14" t="inlineStr">
         <is>
-          <t>00167624</t>
+          <t>00168025</t>
         </is>
       </c>
       <c r="N26" s="15" t="n">
-        <v>344</v>
+        <v>171.4</v>
       </c>
       <c r="O26" s="16" t="n">
         <v>0</v>
@@ -2630,27 +2622,27 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33266</t>
+          <t>PDMDEP-33395</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE CAPBRETON</t>
+          <t>COMMUNE DE MONTBELIARD</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
@@ -2670,7 +2662,7 @@
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J27" s="11" t="n">
@@ -2681,16 +2673,16 @@
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33272</t>
+          <t>PDMDEP-33401</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
         <is>
-          <t>00166910</t>
+          <t>00167624</t>
         </is>
       </c>
       <c r="N27" s="12" t="n">
-        <v>500</v>
+        <v>344</v>
       </c>
       <c r="O27" s="16" t="n">
         <v>0</v>
@@ -2702,27 +2694,27 @@
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-33266</t>
         </is>
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
+          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t>MAIRIE DE CAPBRETON</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>Migracier activité Placier vers Geodp V2</t>
+          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
@@ -2737,12 +2729,12 @@
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I28" s="14" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J28" s="14" t="n">
@@ -2753,16 +2745,16 @@
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33245</t>
+          <t>PDMDEP-33272</t>
         </is>
       </c>
       <c r="M28" s="14" t="inlineStr">
         <is>
-          <t>00166748</t>
+          <t>00166910</t>
         </is>
       </c>
       <c r="N28" s="15" t="n">
-        <v>149</v>
+        <v>500</v>
       </c>
       <c r="O28" s="16" t="n">
         <v>0</v>
@@ -2774,32 +2766,32 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G29" s="11" t="inlineStr">
@@ -2809,12 +2801,12 @@
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J29" s="11" t="n">
@@ -2825,16 +2817,16 @@
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33232</t>
+          <t>PDMDEP-33245</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
-          <t>00166708</t>
+          <t>00166748</t>
         </is>
       </c>
       <c r="N29" s="12" t="n">
-        <v>625</v>
+        <v>149</v>
       </c>
       <c r="O29" s="16" t="n">
         <v>0</v>
@@ -2846,32 +2838,32 @@
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33170</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>Commune de Bonneville</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G30" s="14" t="inlineStr">
@@ -2881,12 +2873,12 @@
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I30" s="14" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J30" s="14" t="n">
@@ -2897,16 +2889,16 @@
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33177</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M30" s="14" t="inlineStr">
         <is>
-          <t>00166356</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N30" s="15" t="n">
-        <v>910</v>
+        <v>625</v>
       </c>
       <c r="O30" s="16" t="n">
         <v>0</v>
@@ -2918,12 +2910,12 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33064</t>
+          <t>PDMDEP-33170</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
@@ -2933,12 +2925,12 @@
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LONGWY</t>
+          <t>Commune de Bonneville</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
@@ -2958,27 +2950,27 @@
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J31" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33073</t>
+          <t>PDMDEP-33177</t>
         </is>
       </c>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>00165708</t>
+          <t>00166356</t>
         </is>
       </c>
       <c r="N31" s="12" t="n">
-        <v>1207</v>
+        <v>910</v>
       </c>
       <c r="O31" s="16" t="n">
         <v>0</v>
@@ -2990,32 +2982,32 @@
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-33064</t>
         </is>
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>MAIRIE DE LONGWY</t>
         </is>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F32" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G32" s="14" t="inlineStr">
@@ -3025,32 +3017,32 @@
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I32" s="14" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="J32" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K32" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-33073</t>
         </is>
       </c>
       <c r="M32" s="14" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00165708</t>
         </is>
       </c>
       <c r="N32" s="15" t="n">
-        <v>500</v>
+        <v>1207</v>
       </c>
       <c r="O32" s="16" t="n">
         <v>0</v>
@@ -3062,27 +3054,27 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32768</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE REIMS</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>MV app/ infra + màj carto</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
@@ -3102,29 +3094,29 @@
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J33" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32772</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M33" s="11" t="inlineStr">
         <is>
-          <t>00163806</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" s="12" t="n">
+        <v>500</v>
+      </c>
+      <c r="O33" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P33" s="12" t="n">
@@ -3134,12 +3126,12 @@
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32768</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
@@ -3149,12 +3141,12 @@
       </c>
       <c r="D34" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>VILLE DE REIMS</t>
         </is>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="F34" s="14" t="inlineStr">
@@ -3174,29 +3166,29 @@
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J34" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K34" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32556</t>
+          <t>PDMDEP-32772</t>
         </is>
       </c>
       <c r="M34" s="14" t="inlineStr">
         <is>
-          <t>00162313</t>
+          <t>00163806</t>
         </is>
       </c>
       <c r="N34" s="15" t="n">
-        <v>142.1</v>
-      </c>
-      <c r="O34" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P34" s="15" t="n">
@@ -3206,32 +3198,32 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G35" s="11" t="inlineStr">
@@ -3241,32 +3233,32 @@
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J35" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K35" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M35" s="11" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N35" s="12" t="n">
-        <v>2335</v>
+        <v>142.1</v>
       </c>
       <c r="O35" s="16" t="n">
         <v>0</v>
@@ -3278,27 +3270,27 @@
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F36" s="14" t="inlineStr">
@@ -3318,7 +3310,7 @@
       </c>
       <c r="I36" s="14" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J36" s="14" t="n">
@@ -3329,16 +3321,16 @@
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M36" s="14" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N36" s="15" t="n">
-        <v>450</v>
+        <v>2335</v>
       </c>
       <c r="O36" s="16" t="n">
         <v>0</v>
@@ -3350,32 +3342,32 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G37" s="11" t="inlineStr">
@@ -3385,32 +3377,32 @@
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J37" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L37" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M37" s="11" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N37" s="12" t="n">
-        <v>910</v>
+        <v>450</v>
       </c>
       <c r="O37" s="16" t="n">
         <v>0</v>
@@ -3422,32 +3414,32 @@
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D38" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
@@ -3457,32 +3449,32 @@
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I38" s="14" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J38" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K38" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M38" s="14" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N38" s="15" t="n">
-        <v>590.15</v>
+        <v>910</v>
       </c>
       <c r="O38" s="16" t="n">
         <v>0</v>
@@ -3494,12 +3486,12 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32086</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
@@ -3509,12 +3501,12 @@
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t>Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
@@ -3529,12 +3521,12 @@
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="J39" s="11" t="n">
@@ -3545,16 +3537,16 @@
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32095</t>
         </is>
       </c>
       <c r="M39" s="11" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00160474</t>
         </is>
       </c>
       <c r="N39" s="12" t="n">
-        <v>285</v>
+        <v>590.15</v>
       </c>
       <c r="O39" s="16" t="n">
         <v>0</v>
@@ -3566,32 +3558,32 @@
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31967</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
@@ -3606,7 +3598,7 @@
       </c>
       <c r="I40" s="14" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J40" s="14" t="n">
@@ -3617,16 +3609,16 @@
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31971</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M40" s="14" t="inlineStr">
         <is>
-          <t>00159863</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N40" s="15" t="n">
-        <v>1325</v>
+        <v>285</v>
       </c>
       <c r="O40" s="16" t="n">
         <v>0</v>
@@ -3638,12 +3630,12 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31967</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
@@ -3653,12 +3645,12 @@
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>DEPARTEMENT DU LOT -CD46</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
@@ -3678,7 +3670,7 @@
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="J41" s="11" t="n">
@@ -3689,16 +3681,16 @@
       </c>
       <c r="L41" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-31971</t>
         </is>
       </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00159863</t>
         </is>
       </c>
       <c r="N41" s="12" t="n">
-        <v>120</v>
+        <v>1325</v>
       </c>
       <c r="O41" s="16" t="n">
         <v>0</v>
@@ -3710,32 +3702,32 @@
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31908</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr">
         <is>
-          <t>Commune de GUINGAMP</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
@@ -3745,7 +3737,7 @@
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I42" s="14" t="inlineStr">
@@ -3761,16 +3753,16 @@
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31917</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M42" s="14" t="inlineStr">
         <is>
-          <t>00159608</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N42" s="15" t="n">
-        <v>588</v>
+        <v>120</v>
       </c>
       <c r="O42" s="16" t="n">
         <v>0</v>
@@ -3782,27 +3774,27 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31908</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>Commune de GUINGAMP</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
@@ -3817,32 +3809,32 @@
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J43" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K43" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L43" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31917</t>
         </is>
       </c>
       <c r="M43" s="11" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00159608</t>
         </is>
       </c>
       <c r="N43" s="12" t="n">
-        <v>203.5</v>
+        <v>588</v>
       </c>
       <c r="O43" s="16" t="n">
         <v>0</v>
@@ -3854,12 +3846,12 @@
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
@@ -3869,12 +3861,12 @@
       </c>
       <c r="D44" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
@@ -3889,12 +3881,12 @@
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I44" s="14" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J44" s="14" t="n">
@@ -3905,16 +3897,16 @@
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31596</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M44" s="14" t="inlineStr">
         <is>
-          <t>00157967</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N44" s="15" t="n">
-        <v>300</v>
+        <v>203.5</v>
       </c>
       <c r="O44" s="16" t="n">
         <v>0</v>
@@ -3926,32 +3918,32 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31589</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G45" s="11" t="inlineStr">
@@ -3961,12 +3953,12 @@
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J45" s="11" t="n">
@@ -3977,16 +3969,16 @@
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31596</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00157967</t>
         </is>
       </c>
       <c r="N45" s="12" t="n">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="O45" s="16" t="n">
         <v>0</v>
@@ -3998,32 +3990,32 @@
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
@@ -4033,12 +4025,12 @@
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I46" s="14" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J46" s="14" t="n">
@@ -4049,16 +4041,16 @@
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31546</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00157816</t>
         </is>
       </c>
       <c r="N46" s="15" t="n">
-        <v>210</v>
+        <v>700</v>
       </c>
       <c r="O46" s="16" t="n">
         <v>0</v>
@@ -4070,12 +4062,12 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
@@ -4085,12 +4077,12 @@
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
@@ -4110,7 +4102,7 @@
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J47" s="11" t="n">
@@ -4121,16 +4113,16 @@
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N47" s="12" t="n">
-        <v>130</v>
+        <v>210</v>
       </c>
       <c r="O47" s="16" t="n">
         <v>0</v>
@@ -4142,12 +4134,12 @@
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
@@ -4157,12 +4149,12 @@
       </c>
       <c r="D48" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F48" s="14" t="inlineStr">
@@ -4182,7 +4174,7 @@
       </c>
       <c r="I48" s="14" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J48" s="14" t="n">
@@ -4193,16 +4185,16 @@
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N48" s="15" t="n">
-        <v>255</v>
+        <v>130</v>
       </c>
       <c r="O48" s="16" t="n">
         <v>0</v>
@@ -4214,12 +4206,12 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
@@ -4229,12 +4221,12 @@
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
@@ -4254,27 +4246,27 @@
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J49" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K49" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N49" s="12" t="n">
-        <v>140</v>
+        <v>255</v>
       </c>
       <c r="O49" s="16" t="n">
         <v>0</v>
@@ -4286,32 +4278,32 @@
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D50" s="14" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G50" s="14" t="inlineStr">
@@ -4321,32 +4313,32 @@
       </c>
       <c r="H50" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I50" s="14" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J50" s="14" t="n">
         <v>8</v>
       </c>
       <c r="K50" s="14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M50" s="14" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N50" s="15" t="n">
-        <v>690</v>
+        <v>140</v>
       </c>
       <c r="O50" s="16" t="n">
         <v>0</v>
@@ -4358,27 +4350,27 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
@@ -4398,27 +4390,27 @@
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J51" s="11" t="n">
         <v>8</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N51" s="12" t="n">
-        <v>187.5</v>
+        <v>690</v>
       </c>
       <c r="O51" s="16" t="n">
         <v>0</v>
@@ -4481,16 +4473,16 @@
       </c>
       <c r="L52" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M52" s="14" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N52" s="15" t="n">
-        <v>787.5</v>
+        <v>187.5</v>
       </c>
       <c r="O52" s="16" t="n">
         <v>0</v>
@@ -4502,32 +4494,32 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>Migration V2</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G53" s="11" t="inlineStr">
@@ -4537,35 +4529,35 @@
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J53" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K53" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N53" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" s="12" t="n">
-        <v>362.5</v>
+        <v>787.5</v>
+      </c>
+      <c r="O53" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P53" s="12" t="n">
         <v>0</v>
@@ -4574,32 +4566,32 @@
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>Commune de CLAMART</t>
         </is>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Migration V2</t>
         </is>
       </c>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G54" s="14" t="inlineStr">
@@ -4609,12 +4601,12 @@
       </c>
       <c r="H54" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I54" s="14" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J54" s="14" t="n">
@@ -4625,19 +4617,19 @@
       </c>
       <c r="L54" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M54" s="14" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N54" s="15" t="n">
-        <v>1320</v>
-      </c>
-      <c r="O54" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O54" s="15" t="n">
+        <v>362.5</v>
       </c>
       <c r="P54" s="15" t="n">
         <v>0</v>
@@ -4646,12 +4638,12 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-26831</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
@@ -4661,38 +4653,54 @@
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>CD74</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>MAJ carto</t>
-        </is>
-      </c>
-      <c r="F55" s="11" t="inlineStr"/>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="F55" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
       <c r="G55" s="11" t="inlineStr">
         <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="H55" s="11" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H55" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J55" s="11" t="n">
         <v>10</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L55" s="11" t="inlineStr"/>
-      <c r="M55" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L55" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28202</t>
+        </is>
+      </c>
+      <c r="M55" s="11" t="inlineStr">
+        <is>
+          <t>00144857</t>
+        </is>
+      </c>
       <c r="N55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" s="12" t="n">
+        <v>1320</v>
+      </c>
+      <c r="O55" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P55" s="12" t="n">
@@ -4702,12 +4710,12 @@
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-26831</t>
         </is>
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
@@ -4717,52 +4725,38 @@
       </c>
       <c r="D56" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
-        </is>
-      </c>
-      <c r="E56" s="14" t="n">
-        <v/>
-      </c>
-      <c r="F56" s="14" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
+          <t>CD74</t>
+        </is>
+      </c>
+      <c r="E56" s="14" t="inlineStr">
+        <is>
+          <t>MAJ carto</t>
+        </is>
+      </c>
+      <c r="F56" s="14" t="inlineStr"/>
       <c r="G56" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H56" s="14" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="H56" s="14" t="inlineStr"/>
       <c r="I56" s="14" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="J56" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K56" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-27017</t>
-        </is>
-      </c>
-      <c r="M56" s="14" t="inlineStr">
-        <is>
-          <t>00141205</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L56" s="14" t="inlineStr"/>
+      <c r="M56" s="14" t="inlineStr"/>
       <c r="N56" s="15" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O56" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P56" s="15" t="n">
@@ -4772,22 +4766,22 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
         </is>
       </c>
       <c r="E57" s="11" t="n">
@@ -4805,32 +4799,32 @@
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J57" s="11" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="K57" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M57" s="11" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N57" s="12" t="n">
-        <v>401</v>
+        <v>1212</v>
       </c>
       <c r="O57" s="16" t="n">
         <v>0</v>
@@ -4842,22 +4836,22 @@
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E58" s="14" t="n">
@@ -4875,34 +4869,34 @@
       </c>
       <c r="H58" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I58" s="14" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J58" s="14" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K58" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M58" s="14" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N58" s="15" t="n">
-        <v>230</v>
-      </c>
-      <c r="O58" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P58" s="15" t="n">
@@ -4912,22 +4906,22 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E59" s="11" t="n">
@@ -4935,7 +4929,7 @@
       </c>
       <c r="F59" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G59" s="11" t="inlineStr">
@@ -4945,32 +4939,32 @@
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J59" s="11" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="K59" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L59" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28019</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M59" s="11" t="inlineStr">
         <is>
-          <t>455151</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N59" s="12" t="n">
-        <v>240</v>
+        <v>401</v>
       </c>
       <c r="O59" s="16" t="n">
         <v>0</v>
@@ -4982,12 +4976,12 @@
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr">
@@ -4997,7 +4991,7 @@
       </c>
       <c r="D60" s="14" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E60" s="14" t="n">
@@ -5015,34 +5009,34 @@
       </c>
       <c r="H60" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I60" s="14" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J60" s="14" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K60" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28023</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M60" s="14" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N60" s="15" t="n">
-        <v>557.145</v>
-      </c>
-      <c r="O60" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P60" s="15" t="n">
@@ -5052,22 +5046,22 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-13128</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>[VALENCIENNES] Littéralis Prime - RAF FAST PARAPHEUR - Déjà facturé</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E61" s="11" t="n">
@@ -5080,31 +5074,39 @@
       </c>
       <c r="G61" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>30/10/2023</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J61" s="11" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L61" s="11" t="inlineStr"/>
-      <c r="M61" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L61" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28034</t>
+        </is>
+      </c>
+      <c r="M61" s="11" t="inlineStr">
+        <is>
+          <t>475575</t>
+        </is>
+      </c>
       <c r="N61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" s="12" t="n">
+        <v>230</v>
+      </c>
+      <c r="O61" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P61" s="12" t="n">
@@ -5114,22 +5116,22 @@
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C62" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D62" s="14" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E62" s="14" t="n">
@@ -5137,32 +5139,44 @@
       </c>
       <c r="F62" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G62" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H62" s="14" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H62" s="14" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
       <c r="I62" s="14" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J62" s="14" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="K62" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L62" s="14" t="inlineStr"/>
-      <c r="M62" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L62" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28019</t>
+        </is>
+      </c>
+      <c r="M62" s="14" t="inlineStr">
+        <is>
+          <t>455151</t>
+        </is>
+      </c>
       <c r="N62" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" s="15" t="n">
+        <v>240</v>
+      </c>
+      <c r="O62" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P62" s="15" t="n">
@@ -5172,89 +5186,349 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
+          <t>PDMDEP-18037</t>
+        </is>
+      </c>
+      <c r="B63" s="11" t="inlineStr">
+        <is>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+        </is>
+      </c>
+      <c r="C63" s="11" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D63" s="11" t="inlineStr">
+        <is>
+          <t>LE PERREUX SUR MARNE</t>
+        </is>
+      </c>
+      <c r="E63" s="11" t="n">
+        <v/>
+      </c>
+      <c r="F63" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G63" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H63" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I63" s="11" t="inlineStr">
+        <is>
+          <t>12/12/2024</t>
+        </is>
+      </c>
+      <c r="J63" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="K63" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M63" s="11" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
+      <c r="N63" s="12" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O63" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-13128</t>
+        </is>
+      </c>
+      <c r="B64" s="14" t="inlineStr">
+        <is>
+          <t>[VALENCIENNES] Littéralis Prime - RAF FAST PARAPHEUR - Déjà facturé</t>
+        </is>
+      </c>
+      <c r="C64" s="14" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="D64" s="14" t="inlineStr">
+        <is>
+          <t>Valenciennes</t>
+        </is>
+      </c>
+      <c r="E64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="F64" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G64" s="14" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H64" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I64" s="14" t="inlineStr">
+        <is>
+          <t>30/10/2023</t>
+        </is>
+      </c>
+      <c r="J64" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="K64" s="14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L64" s="14" t="inlineStr"/>
+      <c r="M64" s="14" t="inlineStr"/>
+      <c r="N64" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-12747</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="inlineStr">
+        <is>
+          <t>[FOUGERES] ARPEGE</t>
+        </is>
+      </c>
+      <c r="C65" s="11" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D65" s="11" t="inlineStr">
+        <is>
+          <t>FOUGERES</t>
+        </is>
+      </c>
+      <c r="E65" s="11" t="n">
+        <v/>
+      </c>
+      <c r="F65" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G65" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H65" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I65" s="11" t="inlineStr">
+        <is>
+          <t>26/09/2023</t>
+        </is>
+      </c>
+      <c r="J65" s="11" t="n">
+        <v>36</v>
+      </c>
+      <c r="K65" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L65" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M65" s="11" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
+      <c r="N65" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-12708</t>
+        </is>
+      </c>
+      <c r="B66" s="14" t="inlineStr">
+        <is>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C66" s="14" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="D66" s="14" t="inlineStr">
+        <is>
+          <t>CD 56 MORBIHAN</t>
+        </is>
+      </c>
+      <c r="E66" s="14" t="n">
+        <v/>
+      </c>
+      <c r="F66" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G66" s="14" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H66" s="14" t="inlineStr"/>
+      <c r="I66" s="14" t="inlineStr">
+        <is>
+          <t>22/09/2023</t>
+        </is>
+      </c>
+      <c r="J66" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="K66" s="14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L66" s="14" t="inlineStr"/>
+      <c r="M66" s="14" t="inlineStr"/>
+      <c r="N66" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="inlineStr">
+        <is>
           <t>PDMDEP-11477</t>
         </is>
       </c>
-      <c r="B63" s="11" t="inlineStr">
+      <c r="B67" s="11" t="inlineStr">
         <is>
           <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
-      <c r="C63" s="11" t="inlineStr"/>
-      <c r="D63" s="11" t="inlineStr">
+      <c r="C67" s="11" t="inlineStr"/>
+      <c r="D67" s="11" t="inlineStr">
         <is>
           <t>MONTPELLIER MMM</t>
         </is>
       </c>
-      <c r="E63" s="11" t="inlineStr">
+      <c r="E67" s="11" t="inlineStr">
         <is>
           <t>Déploiement Module AC</t>
         </is>
       </c>
-      <c r="F63" s="11" t="inlineStr">
+      <c r="F67" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="G63" s="11" t="inlineStr">
+      <c r="G67" s="11" t="inlineStr">
         <is>
           <t>Rework</t>
         </is>
       </c>
-      <c r="H63" s="11" t="inlineStr">
+      <c r="H67" s="11" t="inlineStr">
         <is>
           <t>Nouveau déploiement</t>
         </is>
       </c>
-      <c r="I63" s="11" t="inlineStr">
+      <c r="I67" s="11" t="inlineStr">
         <is>
           <t>03/09/2023</t>
         </is>
       </c>
-      <c r="J63" s="11" t="n">
+      <c r="J67" s="11" t="n">
         <v>36</v>
       </c>
-      <c r="K63" s="11" t="n">
+      <c r="K67" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="L63" s="11" t="inlineStr"/>
-      <c r="M63" s="11" t="inlineStr"/>
-      <c r="N63" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O63" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P63" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="17" t="inlineStr">
+      <c r="L67" s="11" t="inlineStr"/>
+      <c r="M67" s="11" t="inlineStr"/>
+      <c r="N67" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B64" s="17" t="inlineStr"/>
-      <c r="C64" s="17" t="inlineStr"/>
-      <c r="D64" s="17" t="inlineStr"/>
-      <c r="E64" s="17" t="inlineStr"/>
-      <c r="F64" s="17" t="inlineStr"/>
-      <c r="G64" s="17" t="inlineStr"/>
-      <c r="H64" s="17" t="inlineStr"/>
-      <c r="I64" s="17" t="inlineStr"/>
-      <c r="J64" s="17" t="inlineStr"/>
-      <c r="K64" s="17" t="inlineStr"/>
-      <c r="L64" s="17" t="inlineStr"/>
-      <c r="M64" s="17" t="inlineStr"/>
-      <c r="N64" s="18" t="n">
+      <c r="B68" s="17" t="inlineStr"/>
+      <c r="C68" s="17" t="inlineStr"/>
+      <c r="D68" s="17" t="inlineStr"/>
+      <c r="E68" s="17" t="inlineStr"/>
+      <c r="F68" s="17" t="inlineStr"/>
+      <c r="G68" s="17" t="inlineStr"/>
+      <c r="H68" s="17" t="inlineStr"/>
+      <c r="I68" s="17" t="inlineStr"/>
+      <c r="J68" s="17" t="inlineStr"/>
+      <c r="K68" s="17" t="inlineStr"/>
+      <c r="L68" s="17" t="inlineStr"/>
+      <c r="M68" s="17" t="inlineStr"/>
+      <c r="N68" s="18" t="n">
         <v>47526.995</v>
       </c>
-      <c r="O64" s="18" t="n">
+      <c r="O68" s="18" t="n">
         <v>362.5</v>
       </c>
-      <c r="P64" s="18" t="n">
-        <v>25.89</v>
+      <c r="P68" s="18" t="n">
+        <v>21.01</v>
       </c>
     </row>
   </sheetData>
@@ -5319,6 +5593,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A66" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId63"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5893,16 +6171,16 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>1.75</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>10</v>
+        <v>12.25</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>2.5</v>
@@ -5912,7 +6190,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>1.9%</t>
         </is>
       </c>
     </row>
@@ -5923,7 +6201,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>0</v>
@@ -5932,7 +6210,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>2</v>
@@ -5942,7 +6220,7 @@
       </c>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>1.5%</t>
         </is>
       </c>
     </row>
@@ -5954,7 +6232,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>8.75</v>
+        <v>12.5</v>
       </c>
     </row>
   </sheetData>

--- a/jira_export_2026-09-02.xlsx
+++ b/jira_export_2026-09-02.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>34 h</t>
+          <t>39 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P68"/>
+  <dimension ref="A1:P70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -949,7 +949,7 @@
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
     <col width="26" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
@@ -1237,7 +1237,7 @@
         <v>1</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
       <c r="L7" s="11" t="inlineStr"/>
       <c r="M7" s="11" t="inlineStr"/>
@@ -1398,32 +1398,32 @@
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34718</t>
+          <t>PDMDEP-34782</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>[VILLE DE VILLEURBANNE] - Crédits d'heure (14h)</t>
+          <t>[MAIRIE DE SAINT-ISMIER] - Acquisition GEODP Placier</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEURBANNE</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Crédits d'heure (14h)</t>
+          <t>GEODP PLACIER</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -1433,34 +1433,34 @@
       </c>
       <c r="H10" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="J10" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K10" s="14" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="L10" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34722</t>
+          <t>PDMDEP-34791</t>
         </is>
       </c>
       <c r="M10" s="14" t="inlineStr">
         <is>
-          <t>00176875</t>
+          <t>00177122</t>
         </is>
       </c>
       <c r="N10" s="15" t="n">
-        <v>1260</v>
-      </c>
-      <c r="O10" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P10" s="15" t="n">
@@ -1470,32 +1470,32 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34411</t>
+          <t>PDMDEP-34718</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE MAIZIERES LES METZ] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[VILLE DE VILLEURBANNE] - Crédits d'heure (14h)</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE MAIZIERES LES METZ</t>
+          <t>VILLE DE VILLEURBANNE</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>Crédits d'heure (14h)</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
@@ -1505,34 +1505,34 @@
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="J11" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34420</t>
+          <t>PDMDEP-34722</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
         <is>
-          <t>00172317</t>
+          <t>00176875</t>
         </is>
       </c>
       <c r="N11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="12" t="n">
+        <v>1260</v>
+      </c>
+      <c r="O11" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P11" s="12" t="n">
@@ -1542,12 +1542,12 @@
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34319</t>
+          <t>PDMDEP-34411</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
+          <t>[MAIRIE DE MAIZIERES LES METZ] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
@@ -1557,12 +1557,12 @@
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>Commune de Mouscron (BE)</t>
+          <t>MAIRIE DE MAIZIERES LES METZ</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
@@ -1582,29 +1582,29 @@
       </c>
       <c r="I12" s="14" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="J12" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K12" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34326</t>
+          <t>PDMDEP-34420</t>
         </is>
       </c>
       <c r="M12" s="14" t="inlineStr">
         <is>
-          <t>00171691</t>
+          <t>00172317</t>
         </is>
       </c>
       <c r="N12" s="15" t="n">
-        <v>769.5</v>
-      </c>
-      <c r="O12" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P12" s="15" t="n">
@@ -1614,27 +1614,27 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34249</t>
+          <t>PDMDEP-34319</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
+          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIENNE</t>
+          <t>Commune de Mouscron (BE)</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration Placier et ODP </t>
+          <t>Migration GEODP Placier</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="J13" s="11" t="n">
@@ -1665,16 +1665,16 @@
       </c>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34258</t>
+          <t>PDMDEP-34326</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
         <is>
-          <t>00171361</t>
+          <t>00171691</t>
         </is>
       </c>
       <c r="N13" s="12" t="n">
-        <v>2127.2</v>
+        <v>769.5</v>
       </c>
       <c r="O13" s="16" t="n">
         <v>0</v>
@@ -1686,32 +1686,32 @@
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34229</t>
+          <t>PDMDEP-34249</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
+          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>COMMUNE DE VIENNE</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>GRC + Connecteur</t>
+          <t xml:space="preserve">Migration Placier et ODP </t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="H14" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J14" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K14" s="14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34235</t>
+          <t>PDMDEP-34258</t>
         </is>
       </c>
       <c r="M14" s="14" t="inlineStr">
         <is>
-          <t>00171333</t>
+          <t>00171361</t>
         </is>
       </c>
       <c r="N14" s="15" t="n">
-        <v>4536</v>
+        <v>2127.2</v>
       </c>
       <c r="O14" s="16" t="n">
         <v>0</v>
@@ -1758,32 +1758,32 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34208</t>
+          <t>PDMDEP-34229</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
+          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHATEAUGIRON</t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2</t>
+          <t>GRC + Connecteur</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G15" s="11" t="inlineStr">
@@ -1793,32 +1793,32 @@
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="J15" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34216</t>
+          <t>PDMDEP-34235</t>
         </is>
       </c>
       <c r="M15" s="11" t="inlineStr">
         <is>
-          <t>00171155</t>
+          <t>00171333</t>
         </is>
       </c>
       <c r="N15" s="12" t="n">
-        <v>525</v>
+        <v>4536</v>
       </c>
       <c r="O15" s="16" t="n">
         <v>0</v>
@@ -1830,12 +1830,12 @@
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34192</t>
+          <t>PDMDEP-34208</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Macon ] - GEODP Placier</t>
+          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Macon </t>
+          <t>COMMUNE DE CHATEAUGIRON</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>GEODP Placier</t>
+          <t>Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="H16" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I16" s="14" t="inlineStr">
@@ -1877,20 +1877,20 @@
         <v>3</v>
       </c>
       <c r="K16" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34201</t>
+          <t>PDMDEP-34216</t>
         </is>
       </c>
       <c r="M16" s="14" t="inlineStr">
         <is>
-          <t>00171162</t>
+          <t>00171155</t>
         </is>
       </c>
       <c r="N16" s="15" t="n">
-        <v>1662</v>
+        <v>525</v>
       </c>
       <c r="O16" s="16" t="n">
         <v>0</v>
@@ -1902,27 +1902,27 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34169</t>
+          <t>PDMDEP-34192</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[Commune de Macon ] - GEODP Placier</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+          <t xml:space="preserve">Commune de Macon </t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>GEODP Placier</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="J17" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34227</t>
+          <t>PDMDEP-34201</t>
         </is>
       </c>
       <c r="M17" s="11" t="inlineStr">
         <is>
-          <t>2026-0210095</t>
+          <t>00171162</t>
         </is>
       </c>
       <c r="N17" s="12" t="n">
-        <v>9623.1</v>
+        <v>1662</v>
       </c>
       <c r="O17" s="16" t="n">
         <v>0</v>
@@ -1974,12 +1974,12 @@
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34108</t>
+          <t>PDMDEP-34169</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
+          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
@@ -1989,12 +1989,12 @@
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DU PUY EN VELAY</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + migration ODP</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="J18" s="14" t="n">
@@ -2025,16 +2025,16 @@
       </c>
       <c r="L18" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34117</t>
+          <t>PDMDEP-34227</t>
         </is>
       </c>
       <c r="M18" s="14" t="inlineStr">
         <is>
-          <t>00170907</t>
+          <t>2026-0210095</t>
         </is>
       </c>
       <c r="N18" s="15" t="n">
-        <v>707</v>
+        <v>9623.1</v>
       </c>
       <c r="O18" s="16" t="n">
         <v>0</v>
@@ -2046,12 +2046,12 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34064</t>
+          <t>PDMDEP-34108</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
+          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VANNES</t>
+          <t>COMMUNE DU PUY EN VELAY</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
+          <t>Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
@@ -2081,12 +2081,12 @@
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="J19" s="11" t="n">
@@ -2097,16 +2097,16 @@
       </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34070</t>
+          <t>PDMDEP-34117</t>
         </is>
       </c>
       <c r="M19" s="11" t="inlineStr">
         <is>
-          <t>00170468</t>
+          <t>00170907</t>
         </is>
       </c>
       <c r="N19" s="12" t="n">
-        <v>300</v>
+        <v>707</v>
       </c>
       <c r="O19" s="16" t="n">
         <v>0</v>
@@ -2118,27 +2118,27 @@
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33985</t>
+          <t>PDMDEP-34064</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE QUIMPERLE</t>
+          <t>VILLE DE VANNES</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I20" s="14" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="J20" s="14" t="n">
@@ -2169,16 +2169,16 @@
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33991</t>
+          <t>PDMDEP-34070</t>
         </is>
       </c>
       <c r="M20" s="14" t="inlineStr">
         <is>
-          <t>00170408</t>
+          <t>00170468</t>
         </is>
       </c>
       <c r="N20" s="15" t="n">
-        <v>510</v>
+        <v>300</v>
       </c>
       <c r="O20" s="16" t="n">
         <v>0</v>
@@ -2190,32 +2190,32 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33949</t>
+          <t>PDMDEP-33985</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
+          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>Commune de Colmar</t>
+          <t>COMMUNE DE QUIMPERLE</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Modélisation Littéralis Expert</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G21" s="11" t="inlineStr">
@@ -2225,32 +2225,32 @@
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="J21" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33955</t>
+          <t>PDMDEP-33991</t>
         </is>
       </c>
       <c r="M21" s="11" t="inlineStr">
         <is>
-          <t>00170302</t>
+          <t>00170408</t>
         </is>
       </c>
       <c r="N21" s="12" t="n">
-        <v>242.9</v>
+        <v>510</v>
       </c>
       <c r="O21" s="16" t="n">
         <v>0</v>
@@ -2262,27 +2262,27 @@
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33940</t>
+          <t>PDMDEP-33949</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Thionville] - AME </t>
+          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>Commune de Thionville</t>
+          <t>Commune de Colmar</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>AME Littéralis Expert</t>
+          <t>Modélisation Littéralis Expert</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
@@ -2309,20 +2309,20 @@
         <v>3</v>
       </c>
       <c r="K22" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33944</t>
+          <t>PDMDEP-33955</t>
         </is>
       </c>
       <c r="M22" s="14" t="inlineStr">
         <is>
-          <t>00170299</t>
+          <t>00170302</t>
         </is>
       </c>
       <c r="N22" s="15" t="n">
-        <v>220</v>
+        <v>242.9</v>
       </c>
       <c r="O22" s="16" t="n">
         <v>0</v>
@@ -2334,12 +2334,12 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33813</t>
+          <t>PDMDEP-33940</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
+          <t xml:space="preserve">[Commune de Thionville] - AME </t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
@@ -2349,12 +2349,12 @@
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>Commune de Thionville</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>Modélisation Seyne S/ Mer</t>
+          <t>AME Littéralis Expert</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
@@ -2374,29 +2374,29 @@
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J23" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L23" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33817</t>
+          <t>PDMDEP-33944</t>
         </is>
       </c>
       <c r="M23" s="11" t="inlineStr">
         <is>
-          <t>00169865</t>
+          <t>00170299</t>
         </is>
       </c>
       <c r="N23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="O23" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P23" s="12" t="n">
@@ -2406,12 +2406,12 @@
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33804</t>
+          <t>PDMDEP-33813</t>
         </is>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>[CD 73)] - Purge arrêtés temporaires</t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>Purge arrêtés temporaires</t>
+          <t>Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
@@ -2453,22 +2453,22 @@
         <v>3</v>
       </c>
       <c r="K24" s="14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33808</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="M24" s="14" t="inlineStr">
         <is>
-          <t>00169856</t>
+          <t>00169865</t>
         </is>
       </c>
       <c r="N24" s="15" t="n">
-        <v>1890</v>
-      </c>
-      <c r="O24" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P24" s="15" t="n">
@@ -2478,27 +2478,27 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33739</t>
+          <t>PDMDEP-33804</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
+          <t>[CD 73)] - Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>UPSELL PASTELL + DA DPA</t>
+          <t>Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
@@ -2518,27 +2518,27 @@
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J25" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33745</t>
+          <t>PDMDEP-33808</t>
         </is>
       </c>
       <c r="M25" s="11" t="inlineStr">
         <is>
-          <t>00169509</t>
+          <t>00169856</t>
         </is>
       </c>
       <c r="N25" s="12" t="n">
-        <v>920</v>
+        <v>1890</v>
       </c>
       <c r="O25" s="16" t="n">
         <v>0</v>
@@ -2550,27 +2550,27 @@
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33471</t>
+          <t>PDMDEP-33739</t>
         </is>
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
+          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D AUCH</t>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>FDS Facture LiS</t>
+          <t>UPSELL PASTELL + DA DPA</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
@@ -2590,27 +2590,27 @@
       </c>
       <c r="I26" s="14" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J26" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K26" s="14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33475</t>
+          <t>PDMDEP-33745</t>
         </is>
       </c>
       <c r="M26" s="14" t="inlineStr">
         <is>
-          <t>00168025</t>
+          <t>00169509</t>
         </is>
       </c>
       <c r="N26" s="15" t="n">
-        <v>171.4</v>
+        <v>920</v>
       </c>
       <c r="O26" s="16" t="n">
         <v>0</v>
@@ -2622,32 +2622,32 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33395</t>
+          <t>PDMDEP-33471</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBELIARD</t>
+          <t>COMMUNE D AUCH</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t>FDS Facture LiS</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J27" s="11" t="n">
@@ -2673,16 +2673,16 @@
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33401</t>
+          <t>PDMDEP-33475</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
         <is>
-          <t>00167624</t>
+          <t>00168025</t>
         </is>
       </c>
       <c r="N27" s="12" t="n">
-        <v>344</v>
+        <v>171.4</v>
       </c>
       <c r="O27" s="16" t="n">
         <v>0</v>
@@ -2694,27 +2694,27 @@
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33266</t>
+          <t>PDMDEP-33395</t>
         </is>
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE CAPBRETON</t>
+          <t>COMMUNE DE MONTBELIARD</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I28" s="14" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J28" s="14" t="n">
@@ -2745,16 +2745,16 @@
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33272</t>
+          <t>PDMDEP-33401</t>
         </is>
       </c>
       <c r="M28" s="14" t="inlineStr">
         <is>
-          <t>00166910</t>
+          <t>00167624</t>
         </is>
       </c>
       <c r="N28" s="15" t="n">
-        <v>500</v>
+        <v>344</v>
       </c>
       <c r="O28" s="16" t="n">
         <v>0</v>
@@ -2766,27 +2766,27 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-33266</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
+          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t>MAIRIE DE CAPBRETON</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>Migracier activité Placier vers Geodp V2</t>
+          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
@@ -2801,12 +2801,12 @@
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J29" s="11" t="n">
@@ -2817,16 +2817,16 @@
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33245</t>
+          <t>PDMDEP-33272</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
-          <t>00166748</t>
+          <t>00166910</t>
         </is>
       </c>
       <c r="N29" s="12" t="n">
-        <v>149</v>
+        <v>500</v>
       </c>
       <c r="O29" s="16" t="n">
         <v>0</v>
@@ -2838,32 +2838,32 @@
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G30" s="14" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I30" s="14" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J30" s="14" t="n">
@@ -2889,16 +2889,16 @@
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33232</t>
+          <t>PDMDEP-33245</t>
         </is>
       </c>
       <c r="M30" s="14" t="inlineStr">
         <is>
-          <t>00166708</t>
+          <t>00166748</t>
         </is>
       </c>
       <c r="N30" s="15" t="n">
-        <v>625</v>
+        <v>149</v>
       </c>
       <c r="O30" s="16" t="n">
         <v>0</v>
@@ -2910,32 +2910,32 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33170</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>Commune de Bonneville</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G31" s="11" t="inlineStr">
@@ -2945,12 +2945,12 @@
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J31" s="11" t="n">
@@ -2961,16 +2961,16 @@
       </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33177</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>00166356</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N31" s="12" t="n">
-        <v>910</v>
+        <v>625</v>
       </c>
       <c r="O31" s="16" t="n">
         <v>0</v>
@@ -2982,12 +2982,12 @@
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33064</t>
+          <t>PDMDEP-33170</t>
         </is>
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
@@ -2997,12 +2997,12 @@
       </c>
       <c r="D32" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE LONGWY</t>
+          <t>Commune de Bonneville</t>
         </is>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="F32" s="14" t="inlineStr">
@@ -3022,27 +3022,27 @@
       </c>
       <c r="I32" s="14" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J32" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K32" s="14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33073</t>
+          <t>PDMDEP-33177</t>
         </is>
       </c>
       <c r="M32" s="14" t="inlineStr">
         <is>
-          <t>00165708</t>
+          <t>00166356</t>
         </is>
       </c>
       <c r="N32" s="15" t="n">
-        <v>1207</v>
+        <v>910</v>
       </c>
       <c r="O32" s="16" t="n">
         <v>0</v>
@@ -3054,32 +3054,32 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-33064</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>MAIRIE DE LONGWY</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G33" s="11" t="inlineStr">
@@ -3089,32 +3089,32 @@
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="J33" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-33073</t>
         </is>
       </c>
       <c r="M33" s="11" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00165708</t>
         </is>
       </c>
       <c r="N33" s="12" t="n">
-        <v>500</v>
+        <v>1207</v>
       </c>
       <c r="O33" s="16" t="n">
         <v>0</v>
@@ -3126,27 +3126,27 @@
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32768</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE REIMS</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>MV app/ infra + màj carto</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F34" s="14" t="inlineStr">
@@ -3166,29 +3166,29 @@
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J34" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K34" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32772</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M34" s="14" t="inlineStr">
         <is>
-          <t>00163806</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N34" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="15" t="n">
+        <v>500</v>
+      </c>
+      <c r="O34" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P34" s="15" t="n">
@@ -3198,12 +3198,12 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32768</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
@@ -3213,12 +3213,12 @@
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>VILLE DE REIMS</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
@@ -3238,29 +3238,29 @@
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J35" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L35" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32556</t>
+          <t>PDMDEP-32772</t>
         </is>
       </c>
       <c r="M35" s="11" t="inlineStr">
         <is>
-          <t>00162313</t>
+          <t>00163806</t>
         </is>
       </c>
       <c r="N35" s="12" t="n">
-        <v>142.1</v>
-      </c>
-      <c r="O35" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P35" s="12" t="n">
@@ -3270,32 +3270,32 @@
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G36" s="14" t="inlineStr">
@@ -3305,32 +3305,32 @@
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I36" s="14" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J36" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K36" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M36" s="14" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N36" s="15" t="n">
-        <v>2335</v>
+        <v>142.1</v>
       </c>
       <c r="O36" s="16" t="n">
         <v>0</v>
@@ -3342,27 +3342,27 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J37" s="11" t="n">
@@ -3393,16 +3393,16 @@
       </c>
       <c r="L37" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M37" s="11" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N37" s="12" t="n">
-        <v>450</v>
+        <v>2335</v>
       </c>
       <c r="O37" s="16" t="n">
         <v>0</v>
@@ -3414,32 +3414,32 @@
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D38" s="14" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
@@ -3449,32 +3449,32 @@
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I38" s="14" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J38" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K38" s="14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M38" s="14" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N38" s="15" t="n">
-        <v>910</v>
+        <v>450</v>
       </c>
       <c r="O38" s="16" t="n">
         <v>0</v>
@@ -3486,32 +3486,32 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G39" s="11" t="inlineStr">
@@ -3521,32 +3521,32 @@
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J39" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M39" s="11" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N39" s="12" t="n">
-        <v>590.15</v>
+        <v>910</v>
       </c>
       <c r="O39" s="16" t="n">
         <v>0</v>
@@ -3558,12 +3558,12 @@
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32086</t>
         </is>
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
@@ -3573,12 +3573,12 @@
       </c>
       <c r="D40" s="14" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
         </is>
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t>Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="F40" s="14" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I40" s="14" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="J40" s="14" t="n">
@@ -3609,16 +3609,16 @@
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32095</t>
         </is>
       </c>
       <c r="M40" s="14" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00160474</t>
         </is>
       </c>
       <c r="N40" s="15" t="n">
-        <v>285</v>
+        <v>590.15</v>
       </c>
       <c r="O40" s="16" t="n">
         <v>0</v>
@@ -3630,32 +3630,32 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31967</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G41" s="11" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J41" s="11" t="n">
@@ -3681,16 +3681,16 @@
       </c>
       <c r="L41" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31971</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>00159863</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N41" s="12" t="n">
-        <v>1325</v>
+        <v>285</v>
       </c>
       <c r="O41" s="16" t="n">
         <v>0</v>
@@ -3702,12 +3702,12 @@
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31967</t>
         </is>
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
@@ -3717,12 +3717,12 @@
       </c>
       <c r="D42" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>DEPARTEMENT DU LOT -CD46</t>
         </is>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="F42" s="14" t="inlineStr">
@@ -3742,7 +3742,7 @@
       </c>
       <c r="I42" s="14" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="J42" s="14" t="n">
@@ -3753,16 +3753,16 @@
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-31971</t>
         </is>
       </c>
       <c r="M42" s="14" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00159863</t>
         </is>
       </c>
       <c r="N42" s="15" t="n">
-        <v>120</v>
+        <v>1325</v>
       </c>
       <c r="O42" s="16" t="n">
         <v>0</v>
@@ -3774,32 +3774,32 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31908</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>Commune de GUINGAMP</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G43" s="11" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I43" s="11" t="inlineStr">
@@ -3825,16 +3825,16 @@
       </c>
       <c r="L43" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31917</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M43" s="11" t="inlineStr">
         <is>
-          <t>00159608</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N43" s="12" t="n">
-        <v>588</v>
+        <v>120</v>
       </c>
       <c r="O43" s="16" t="n">
         <v>0</v>
@@ -3846,27 +3846,27 @@
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31908</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>Commune de GUINGAMP</t>
         </is>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
@@ -3881,32 +3881,32 @@
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I44" s="14" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J44" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K44" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31917</t>
         </is>
       </c>
       <c r="M44" s="14" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00159608</t>
         </is>
       </c>
       <c r="N44" s="15" t="n">
-        <v>203.5</v>
+        <v>588</v>
       </c>
       <c r="O44" s="16" t="n">
         <v>0</v>
@@ -3918,12 +3918,12 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J45" s="11" t="n">
@@ -3969,16 +3969,16 @@
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31596</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
         <is>
-          <t>00157967</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N45" s="12" t="n">
-        <v>300</v>
+        <v>203.5</v>
       </c>
       <c r="O45" s="16" t="n">
         <v>0</v>
@@ -3990,32 +3990,32 @@
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31589</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
@@ -4025,12 +4025,12 @@
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I46" s="14" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J46" s="14" t="n">
@@ -4041,16 +4041,16 @@
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31596</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00157967</t>
         </is>
       </c>
       <c r="N46" s="15" t="n">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="O46" s="16" t="n">
         <v>0</v>
@@ -4062,32 +4062,32 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G47" s="11" t="inlineStr">
@@ -4097,12 +4097,12 @@
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J47" s="11" t="n">
@@ -4113,16 +4113,16 @@
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31546</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00157816</t>
         </is>
       </c>
       <c r="N47" s="12" t="n">
-        <v>210</v>
+        <v>700</v>
       </c>
       <c r="O47" s="16" t="n">
         <v>0</v>
@@ -4134,12 +4134,12 @@
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
@@ -4149,12 +4149,12 @@
       </c>
       <c r="D48" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F48" s="14" t="inlineStr">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="I48" s="14" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J48" s="14" t="n">
@@ -4185,16 +4185,16 @@
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N48" s="15" t="n">
-        <v>130</v>
+        <v>210</v>
       </c>
       <c r="O48" s="16" t="n">
         <v>0</v>
@@ -4206,12 +4206,12 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J49" s="11" t="n">
@@ -4257,16 +4257,16 @@
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N49" s="12" t="n">
-        <v>255</v>
+        <v>130</v>
       </c>
       <c r="O49" s="16" t="n">
         <v>0</v>
@@ -4278,12 +4278,12 @@
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
@@ -4293,12 +4293,12 @@
       </c>
       <c r="D50" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F50" s="14" t="inlineStr">
@@ -4318,27 +4318,27 @@
       </c>
       <c r="I50" s="14" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J50" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K50" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M50" s="14" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N50" s="15" t="n">
-        <v>140</v>
+        <v>255</v>
       </c>
       <c r="O50" s="16" t="n">
         <v>0</v>
@@ -4350,32 +4350,32 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
@@ -4385,32 +4385,32 @@
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J51" s="11" t="n">
         <v>8</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N51" s="12" t="n">
-        <v>690</v>
+        <v>140</v>
       </c>
       <c r="O51" s="16" t="n">
         <v>0</v>
@@ -4422,27 +4422,27 @@
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D52" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr">
@@ -4462,27 +4462,27 @@
       </c>
       <c r="I52" s="14" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J52" s="14" t="n">
         <v>8</v>
       </c>
       <c r="K52" s="14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L52" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M52" s="14" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N52" s="15" t="n">
-        <v>187.5</v>
+        <v>690</v>
       </c>
       <c r="O52" s="16" t="n">
         <v>0</v>
@@ -4545,16 +4545,16 @@
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N53" s="12" t="n">
-        <v>787.5</v>
+        <v>187.5</v>
       </c>
       <c r="O53" s="16" t="n">
         <v>0</v>
@@ -4566,32 +4566,32 @@
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>Migration V2</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G54" s="14" t="inlineStr">
@@ -4601,35 +4601,35 @@
       </c>
       <c r="H54" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I54" s="14" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J54" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K54" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L54" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M54" s="14" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N54" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" s="15" t="n">
-        <v>362.5</v>
+        <v>787.5</v>
+      </c>
+      <c r="O54" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P54" s="15" t="n">
         <v>0</v>
@@ -4638,32 +4638,32 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>Commune de CLAMART</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Migration V2</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G55" s="11" t="inlineStr">
@@ -4673,12 +4673,12 @@
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J55" s="11" t="n">
@@ -4689,19 +4689,19 @@
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M55" s="11" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N55" s="12" t="n">
-        <v>1320</v>
-      </c>
-      <c r="O55" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O55" s="12" t="n">
+        <v>362.5</v>
       </c>
       <c r="P55" s="12" t="n">
         <v>0</v>
@@ -4710,12 +4710,12 @@
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-26831</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
@@ -4725,38 +4725,54 @@
       </c>
       <c r="D56" s="14" t="inlineStr">
         <is>
-          <t>CD74</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>MAJ carto</t>
-        </is>
-      </c>
-      <c r="F56" s="14" t="inlineStr"/>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="F56" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
       <c r="G56" s="14" t="inlineStr">
         <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="H56" s="14" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H56" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I56" s="14" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J56" s="14" t="n">
         <v>10</v>
       </c>
       <c r="K56" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L56" s="14" t="inlineStr"/>
-      <c r="M56" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L56" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28202</t>
+        </is>
+      </c>
+      <c r="M56" s="14" t="inlineStr">
+        <is>
+          <t>00144857</t>
+        </is>
+      </c>
       <c r="N56" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" s="15" t="n">
+        <v>1320</v>
+      </c>
+      <c r="O56" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P56" s="15" t="n">
@@ -4766,12 +4782,12 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-26831</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
@@ -4781,52 +4797,38 @@
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
-        </is>
-      </c>
-      <c r="E57" s="11" t="n">
-        <v/>
-      </c>
-      <c r="F57" s="11" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
+          <t>CD74</t>
+        </is>
+      </c>
+      <c r="E57" s="11" t="inlineStr">
+        <is>
+          <t>MAJ carto</t>
+        </is>
+      </c>
+      <c r="F57" s="11" t="inlineStr"/>
       <c r="G57" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H57" s="11" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="H57" s="11" t="inlineStr"/>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="J57" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K57" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-27017</t>
-        </is>
-      </c>
-      <c r="M57" s="11" t="inlineStr">
-        <is>
-          <t>00141205</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L57" s="11" t="inlineStr"/>
+      <c r="M57" s="11" t="inlineStr"/>
       <c r="N57" s="12" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O57" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P57" s="12" t="n">
@@ -4836,12 +4838,12 @@
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
@@ -4851,7 +4853,7 @@
       </c>
       <c r="D58" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
         </is>
       </c>
       <c r="E58" s="14" t="n">
@@ -4874,29 +4876,29 @@
       </c>
       <c r="I58" s="14" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J58" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K58" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M58" s="14" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N58" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" s="15" t="n">
+        <v>1212</v>
+      </c>
+      <c r="O58" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P58" s="15" t="n">
@@ -4906,22 +4908,22 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E59" s="11" t="n">
@@ -4939,34 +4941,34 @@
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J59" s="11" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K59" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M59" s="11" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N59" s="12" t="n">
-        <v>401</v>
-      </c>
-      <c r="O59" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P59" s="12" t="n">
@@ -4976,12 +4978,12 @@
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr">
@@ -4991,7 +4993,7 @@
       </c>
       <c r="D60" s="14" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E60" s="14" t="n">
@@ -5009,34 +5011,34 @@
       </c>
       <c r="H60" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I60" s="14" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J60" s="14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K60" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M60" s="14" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N60" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" s="15" t="n">
+        <v>401</v>
+      </c>
+      <c r="O60" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P60" s="15" t="n">
@@ -5046,12 +5048,12 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
@@ -5061,7 +5063,7 @@
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E61" s="11" t="n">
@@ -5079,34 +5081,34 @@
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J61" s="11" t="n">
         <v>17</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L61" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M61" s="11" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N61" s="12" t="n">
-        <v>230</v>
-      </c>
-      <c r="O61" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P61" s="12" t="n">
@@ -5116,22 +5118,22 @@
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C62" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D62" s="14" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E62" s="14" t="n">
@@ -5139,7 +5141,7 @@
       </c>
       <c r="F62" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G62" s="14" t="inlineStr">
@@ -5149,32 +5151,32 @@
       </c>
       <c r="H62" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I62" s="14" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J62" s="14" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K62" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L62" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28019</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M62" s="14" t="inlineStr">
         <is>
-          <t>455151</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N62" s="15" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="O62" s="16" t="n">
         <v>0</v>
@@ -5186,12 +5188,12 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
@@ -5201,7 +5203,7 @@
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E63" s="11" t="n">
@@ -5214,39 +5216,31 @@
       </c>
       <c r="G63" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J63" s="11" t="n">
         <v>21</v>
       </c>
       <c r="K63" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28023</t>
-        </is>
-      </c>
-      <c r="M63" s="11" t="inlineStr">
-        <is>
-          <t>454387</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L63" s="11" t="inlineStr"/>
+      <c r="M63" s="11" t="inlineStr"/>
       <c r="N63" s="12" t="n">
-        <v>557.145</v>
-      </c>
-      <c r="O63" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P63" s="12" t="n">
@@ -5256,22 +5250,22 @@
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-13128</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t>[VALENCIENNES] Littéralis Prime - RAF FAST PARAPHEUR - Déjà facturé</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D64" s="14" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E64" s="14" t="n">
@@ -5279,36 +5273,44 @@
       </c>
       <c r="F64" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G64" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H64" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I64" s="14" t="inlineStr">
         <is>
-          <t>30/10/2023</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J64" s="14" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="K64" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L64" s="14" t="inlineStr"/>
-      <c r="M64" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L64" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28019</t>
+        </is>
+      </c>
+      <c r="M64" s="14" t="inlineStr">
+        <is>
+          <t>455151</t>
+        </is>
+      </c>
       <c r="N64" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" s="15" t="n">
+        <v>240</v>
+      </c>
+      <c r="O64" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P64" s="15" t="n">
@@ -5318,12 +5320,12 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
@@ -5333,7 +5335,7 @@
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E65" s="11" t="n">
@@ -5356,29 +5358,29 @@
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J65" s="11" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="K65" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27990</t>
+          <t>PDMDEP-28023</t>
         </is>
       </c>
       <c r="M65" s="11" t="inlineStr">
         <is>
-          <t>406296</t>
+          <t>454387</t>
         </is>
       </c>
       <c r="N65" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O65" s="12" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O65" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P65" s="12" t="n">
@@ -5388,12 +5390,12 @@
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-13128</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[VALENCIENNES] Littéralis Prime - RAF FAST PARAPHEUR - Déjà facturé</t>
         </is>
       </c>
       <c r="C66" s="14" t="inlineStr">
@@ -5403,7 +5405,7 @@
       </c>
       <c r="D66" s="14" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="E66" s="14" t="n">
@@ -5419,17 +5421,21 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H66" s="14" t="inlineStr"/>
+      <c r="H66" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I66" s="14" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>30/10/2023</t>
         </is>
       </c>
       <c r="J66" s="14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K66" s="14" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L66" s="14" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -5446,24 +5452,26 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C67" s="11" t="inlineStr"/>
+          <t>[FOUGERES] ARPEGE</t>
+        </is>
+      </c>
+      <c r="C67" s="11" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E67" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>FOUGERES</t>
+        </is>
+      </c>
+      <c r="E67" s="11" t="n">
+        <v/>
       </c>
       <c r="F67" s="11" t="inlineStr">
         <is>
@@ -5472,63 +5480,189 @@
       </c>
       <c r="G67" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J67" s="11" t="n">
         <v>36</v>
       </c>
       <c r="K67" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L67" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M67" s="11" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
+      <c r="N67" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-12708</t>
+        </is>
+      </c>
+      <c r="B68" s="14" t="inlineStr">
+        <is>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C68" s="14" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="D68" s="14" t="inlineStr">
+        <is>
+          <t>CD 56 MORBIHAN</t>
+        </is>
+      </c>
+      <c r="E68" s="14" t="n">
+        <v/>
+      </c>
+      <c r="F68" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G68" s="14" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H68" s="14" t="inlineStr"/>
+      <c r="I68" s="14" t="inlineStr">
+        <is>
+          <t>22/09/2023</t>
+        </is>
+      </c>
+      <c r="J68" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="K68" s="14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L68" s="14" t="inlineStr"/>
+      <c r="M68" s="14" t="inlineStr"/>
+      <c r="N68" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-11477</t>
+        </is>
+      </c>
+      <c r="B69" s="11" t="inlineStr">
+        <is>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C69" s="11" t="inlineStr"/>
+      <c r="D69" s="11" t="inlineStr">
+        <is>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E69" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
+      <c r="F69" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G69" s="11" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H69" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I69" s="11" t="inlineStr">
+        <is>
+          <t>03/09/2023</t>
+        </is>
+      </c>
+      <c r="J69" s="11" t="n">
+        <v>36</v>
+      </c>
+      <c r="K69" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="L67" s="11" t="inlineStr"/>
-      <c r="M67" s="11" t="inlineStr"/>
-      <c r="N67" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O67" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P67" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="17" t="inlineStr">
+      <c r="L69" s="11" t="inlineStr"/>
+      <c r="M69" s="11" t="inlineStr"/>
+      <c r="N69" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B68" s="17" t="inlineStr"/>
-      <c r="C68" s="17" t="inlineStr"/>
-      <c r="D68" s="17" t="inlineStr"/>
-      <c r="E68" s="17" t="inlineStr"/>
-      <c r="F68" s="17" t="inlineStr"/>
-      <c r="G68" s="17" t="inlineStr"/>
-      <c r="H68" s="17" t="inlineStr"/>
-      <c r="I68" s="17" t="inlineStr"/>
-      <c r="J68" s="17" t="inlineStr"/>
-      <c r="K68" s="17" t="inlineStr"/>
-      <c r="L68" s="17" t="inlineStr"/>
-      <c r="M68" s="17" t="inlineStr"/>
-      <c r="N68" s="18" t="n">
+      <c r="B70" s="17" t="inlineStr"/>
+      <c r="C70" s="17" t="inlineStr"/>
+      <c r="D70" s="17" t="inlineStr"/>
+      <c r="E70" s="17" t="inlineStr"/>
+      <c r="F70" s="17" t="inlineStr"/>
+      <c r="G70" s="17" t="inlineStr"/>
+      <c r="H70" s="17" t="inlineStr"/>
+      <c r="I70" s="17" t="inlineStr"/>
+      <c r="J70" s="17" t="inlineStr"/>
+      <c r="K70" s="17" t="inlineStr"/>
+      <c r="L70" s="17" t="inlineStr"/>
+      <c r="M70" s="17" t="inlineStr"/>
+      <c r="N70" s="18" t="n">
         <v>47526.995</v>
       </c>
-      <c r="O68" s="18" t="n">
+      <c r="O70" s="18" t="n">
         <v>362.5</v>
       </c>
-      <c r="P68" s="18" t="n">
-        <v>21.01</v>
+      <c r="P70" s="18" t="n">
+        <v>16.67</v>
       </c>
     </row>
   </sheetData>
@@ -5597,6 +5731,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId61"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A66" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId65"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6171,16 +6307,16 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>12.25</v>
+        <v>14.75</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>2.5</v>
@@ -6190,7 +6326,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
     </row>
@@ -6201,7 +6337,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>0</v>
@@ -6210,7 +6346,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>2</v>
@@ -6220,7 +6356,7 @@
       </c>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>2.2%</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6368,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -6320,10 +6456,10 @@
         <v>366023</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>137842</v>
+        <v>133933</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>228181</v>
+        <v>232090</v>
       </c>
       <c r="E5" s="24" t="n">
         <v>144874</v>
@@ -6332,7 +6468,7 @@
         <v>21179</v>
       </c>
       <c r="G5" s="24" t="n">
-        <v>24677</v>
+        <v>28586</v>
       </c>
     </row>
     <row r="6">
@@ -6370,10 +6506,10 @@
         <v>201740</v>
       </c>
       <c r="C7" s="26" t="n">
-        <v>77207</v>
+        <v>73297</v>
       </c>
       <c r="D7" s="26" t="n">
-        <v>124534</v>
+        <v>128443</v>
       </c>
       <c r="E7" s="26" t="n">
         <v>58244</v>
@@ -6382,7 +6518,7 @@
         <v>9871</v>
       </c>
       <c r="G7" s="26" t="n">
-        <v>21492</v>
+        <v>25401</v>
       </c>
     </row>
   </sheetData>
@@ -6514,7 +6650,7 @@
         </is>
       </c>
       <c r="I5" s="25" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="6">
@@ -6580,7 +6716,7 @@
         </is>
       </c>
       <c r="I7" s="24" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="8">
@@ -6622,7 +6758,7 @@
         </is>
       </c>
       <c r="I9" s="24" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
     </row>
   </sheetData>

--- a/jira_export_2026-09-02.xlsx
+++ b/jira_export_2026-09-02.xlsx
@@ -720,7 +720,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>362 €</t>
+          <t>1,265 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +734,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -760,7 +760,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>0 €</t>
+          <t>903 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>39 h</t>
+          <t>53 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -900,7 +900,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>266</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -933,13 +933,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P70"/>
+  <dimension ref="A1:P79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="27" customWidth="1" min="7" max="7"/>
@@ -949,7 +949,7 @@
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
     <col width="26" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
@@ -1117,10 +1117,10 @@
         <v>0</v>
       </c>
       <c r="O5" s="12" t="n">
-        <v>0</v>
+        <v>902.72</v>
       </c>
       <c r="P5" s="12" t="n">
-        <v>0</v>
+        <v>451.36</v>
       </c>
     </row>
     <row r="6">
@@ -1517,7 +1517,7 @@
         <v>2</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
@@ -1686,27 +1686,27 @@
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34249</t>
+          <t>PDMDEP-34287</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
+          <t xml:space="preserve">[COMMUNE DE LUNEL] - Migration GeODP </t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIENNE</t>
+          <t>COMMUNE DE LUNEL</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration Placier et ODP </t>
+          <t xml:space="preserve">Migration GeODP </t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H14" s="14" t="inlineStr">
@@ -1733,22 +1733,14 @@
         <v>3</v>
       </c>
       <c r="K14" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34258</t>
-        </is>
-      </c>
-      <c r="M14" s="14" t="inlineStr">
-        <is>
-          <t>00171361</t>
-        </is>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="L14" s="14" t="inlineStr"/>
+      <c r="M14" s="14" t="inlineStr"/>
       <c r="N14" s="15" t="n">
-        <v>2127.2</v>
-      </c>
-      <c r="O14" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P14" s="15" t="n">
@@ -1758,32 +1750,32 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34229</t>
+          <t>PDMDEP-34249</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
+          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>COMMUNE DE VIENNE</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>GRC + Connecteur</t>
+          <t xml:space="preserve">Migration Placier et ODP </t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G15" s="11" t="inlineStr">
@@ -1793,32 +1785,32 @@
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J15" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34235</t>
+          <t>PDMDEP-34258</t>
         </is>
       </c>
       <c r="M15" s="11" t="inlineStr">
         <is>
-          <t>00171333</t>
+          <t>00171361</t>
         </is>
       </c>
       <c r="N15" s="12" t="n">
-        <v>4536</v>
+        <v>2127.2</v>
       </c>
       <c r="O15" s="16" t="n">
         <v>0</v>
@@ -1830,32 +1822,32 @@
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34208</t>
+          <t>PDMDEP-34229</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
+          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHATEAUGIRON</t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2</t>
+          <t>GRC + Connecteur</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -1865,32 +1857,32 @@
       </c>
       <c r="H16" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I16" s="14" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="J16" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K16" s="14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L16" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34216</t>
+          <t>PDMDEP-34235</t>
         </is>
       </c>
       <c r="M16" s="14" t="inlineStr">
         <is>
-          <t>00171155</t>
+          <t>00171333</t>
         </is>
       </c>
       <c r="N16" s="15" t="n">
-        <v>525</v>
+        <v>4536</v>
       </c>
       <c r="O16" s="16" t="n">
         <v>0</v>
@@ -1902,12 +1894,12 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34192</t>
+          <t>PDMDEP-34208</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Macon ] - GEODP Placier</t>
+          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
@@ -1917,12 +1909,12 @@
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Macon </t>
+          <t>COMMUNE DE CHATEAUGIRON</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>GEODP Placier</t>
+          <t>Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
@@ -1937,7 +1929,7 @@
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I17" s="11" t="inlineStr">
@@ -1949,20 +1941,20 @@
         <v>3</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34201</t>
+          <t>PDMDEP-34216</t>
         </is>
       </c>
       <c r="M17" s="11" t="inlineStr">
         <is>
-          <t>00171162</t>
+          <t>00171155</t>
         </is>
       </c>
       <c r="N17" s="12" t="n">
-        <v>1662</v>
+        <v>525</v>
       </c>
       <c r="O17" s="16" t="n">
         <v>0</v>
@@ -1974,27 +1966,27 @@
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34169</t>
+          <t>PDMDEP-34192</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[Commune de Macon ] - GEODP Placier</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+          <t xml:space="preserve">Commune de Macon </t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>GEODP Placier</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
@@ -2009,32 +2001,32 @@
       </c>
       <c r="H18" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="J18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K18" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34227</t>
+          <t>PDMDEP-34201</t>
         </is>
       </c>
       <c r="M18" s="14" t="inlineStr">
         <is>
-          <t>2026-0210095</t>
+          <t>00171162</t>
         </is>
       </c>
       <c r="N18" s="15" t="n">
-        <v>9623.1</v>
+        <v>1662</v>
       </c>
       <c r="O18" s="16" t="n">
         <v>0</v>
@@ -2046,12 +2038,12 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34108</t>
+          <t>PDMDEP-34169</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
+          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
@@ -2061,12 +2053,12 @@
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DU PUY EN VELAY</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + migration ODP</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
@@ -2086,7 +2078,7 @@
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="J19" s="11" t="n">
@@ -2097,16 +2089,16 @@
       </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34117</t>
+          <t>PDMDEP-34227</t>
         </is>
       </c>
       <c r="M19" s="11" t="inlineStr">
         <is>
-          <t>00170907</t>
+          <t>2026-0210095</t>
         </is>
       </c>
       <c r="N19" s="12" t="n">
-        <v>707</v>
+        <v>9623.1</v>
       </c>
       <c r="O19" s="16" t="n">
         <v>0</v>
@@ -2118,12 +2110,12 @@
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34064</t>
+          <t>PDMDEP-34108</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
+          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
@@ -2133,12 +2125,12 @@
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE VANNES</t>
+          <t>COMMUNE DU PUY EN VELAY</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
+          <t>Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
@@ -2153,12 +2145,12 @@
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I20" s="14" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="J20" s="14" t="n">
@@ -2169,16 +2161,16 @@
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34070</t>
+          <t>PDMDEP-34117</t>
         </is>
       </c>
       <c r="M20" s="14" t="inlineStr">
         <is>
-          <t>00170468</t>
+          <t>00170907</t>
         </is>
       </c>
       <c r="N20" s="15" t="n">
-        <v>300</v>
+        <v>707</v>
       </c>
       <c r="O20" s="16" t="n">
         <v>0</v>
@@ -2190,27 +2182,27 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33985</t>
+          <t>PDMDEP-34064</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE QUIMPERLE</t>
+          <t>VILLE DE VANNES</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
@@ -2225,12 +2217,12 @@
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="J21" s="11" t="n">
@@ -2241,16 +2233,16 @@
       </c>
       <c r="L21" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33991</t>
+          <t>PDMDEP-34070</t>
         </is>
       </c>
       <c r="M21" s="11" t="inlineStr">
         <is>
-          <t>00170408</t>
+          <t>00170468</t>
         </is>
       </c>
       <c r="N21" s="12" t="n">
-        <v>510</v>
+        <v>300</v>
       </c>
       <c r="O21" s="16" t="n">
         <v>0</v>
@@ -2262,32 +2254,32 @@
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33949</t>
+          <t>PDMDEP-33985</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
+          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>Commune de Colmar</t>
+          <t>COMMUNE DE QUIMPERLE</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>Modélisation Littéralis Expert</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
@@ -2297,32 +2289,32 @@
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I22" s="14" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="J22" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K22" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33955</t>
+          <t>PDMDEP-33991</t>
         </is>
       </c>
       <c r="M22" s="14" t="inlineStr">
         <is>
-          <t>00170302</t>
+          <t>00170408</t>
         </is>
       </c>
       <c r="N22" s="15" t="n">
-        <v>242.9</v>
+        <v>510</v>
       </c>
       <c r="O22" s="16" t="n">
         <v>0</v>
@@ -2334,27 +2326,27 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33940</t>
+          <t>PDMDEP-33949</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Thionville] - AME </t>
+          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>Commune de Thionville</t>
+          <t>Commune de Colmar</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>AME Littéralis Expert</t>
+          <t>Modélisation Littéralis Expert</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
@@ -2381,20 +2373,20 @@
         <v>3</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33944</t>
+          <t>PDMDEP-33955</t>
         </is>
       </c>
       <c r="M23" s="11" t="inlineStr">
         <is>
-          <t>00170299</t>
+          <t>00170302</t>
         </is>
       </c>
       <c r="N23" s="12" t="n">
-        <v>220</v>
+        <v>242.9</v>
       </c>
       <c r="O23" s="16" t="n">
         <v>0</v>
@@ -2406,12 +2398,12 @@
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33813</t>
+          <t>PDMDEP-33940</t>
         </is>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
+          <t xml:space="preserve">[Commune de Thionville] - AME </t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
@@ -2421,12 +2413,12 @@
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>Commune de Thionville</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>Modélisation Seyne S/ Mer</t>
+          <t>AME Littéralis Expert</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
@@ -2446,29 +2438,29 @@
       </c>
       <c r="I24" s="14" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J24" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K24" s="14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33817</t>
+          <t>PDMDEP-33944</t>
         </is>
       </c>
       <c r="M24" s="14" t="inlineStr">
         <is>
-          <t>00169865</t>
+          <t>00170299</t>
         </is>
       </c>
       <c r="N24" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="15" t="n">
+        <v>220</v>
+      </c>
+      <c r="O24" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P24" s="15" t="n">
@@ -2478,12 +2470,12 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33804</t>
+          <t>PDMDEP-33813</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>[CD 73)] - Purge arrêtés temporaires</t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
@@ -2493,12 +2485,12 @@
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>Purge arrêtés temporaires</t>
+          <t>Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
@@ -2525,22 +2517,22 @@
         <v>3</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33808</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="M25" s="11" t="inlineStr">
         <is>
-          <t>00169856</t>
+          <t>00169865</t>
         </is>
       </c>
       <c r="N25" s="12" t="n">
-        <v>1890</v>
-      </c>
-      <c r="O25" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P25" s="12" t="n">
@@ -2550,27 +2542,27 @@
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33739</t>
+          <t>PDMDEP-33804</t>
         </is>
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
+          <t>[CD 73)] - Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>UPSELL PASTELL + DA DPA</t>
+          <t>Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
@@ -2590,27 +2582,27 @@
       </c>
       <c r="I26" s="14" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J26" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K26" s="14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33745</t>
+          <t>PDMDEP-33808</t>
         </is>
       </c>
       <c r="M26" s="14" t="inlineStr">
         <is>
-          <t>00169509</t>
+          <t>00169856</t>
         </is>
       </c>
       <c r="N26" s="15" t="n">
-        <v>920</v>
+        <v>1890</v>
       </c>
       <c r="O26" s="16" t="n">
         <v>0</v>
@@ -2622,27 +2614,27 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33471</t>
+          <t>PDMDEP-33739</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
+          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D AUCH</t>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>FDS Facture LiS</t>
+          <t>UPSELL PASTELL + DA DPA</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
@@ -2662,27 +2654,27 @@
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J27" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33475</t>
+          <t>PDMDEP-33745</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
         <is>
-          <t>00168025</t>
+          <t>00169509</t>
         </is>
       </c>
       <c r="N27" s="12" t="n">
-        <v>171.4</v>
+        <v>920</v>
       </c>
       <c r="O27" s="16" t="n">
         <v>0</v>
@@ -2694,32 +2686,32 @@
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33395</t>
+          <t>PDMDEP-33471</t>
         </is>
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
         </is>
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBELIARD</t>
+          <t>COMMUNE D AUCH</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t>FDS Facture LiS</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G28" s="14" t="inlineStr">
@@ -2734,7 +2726,7 @@
       </c>
       <c r="I28" s="14" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J28" s="14" t="n">
@@ -2745,16 +2737,16 @@
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33401</t>
+          <t>PDMDEP-33475</t>
         </is>
       </c>
       <c r="M28" s="14" t="inlineStr">
         <is>
-          <t>00167624</t>
+          <t>00168025</t>
         </is>
       </c>
       <c r="N28" s="15" t="n">
-        <v>344</v>
+        <v>171.4</v>
       </c>
       <c r="O28" s="16" t="n">
         <v>0</v>
@@ -2766,27 +2758,27 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33266</t>
+          <t>PDMDEP-33395</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE CAPBRETON</t>
+          <t>COMMUNE DE MONTBELIARD</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
@@ -2806,7 +2798,7 @@
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J29" s="11" t="n">
@@ -2817,16 +2809,16 @@
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33272</t>
+          <t>PDMDEP-33401</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
-          <t>00166910</t>
+          <t>00167624</t>
         </is>
       </c>
       <c r="N29" s="12" t="n">
-        <v>500</v>
+        <v>344</v>
       </c>
       <c r="O29" s="16" t="n">
         <v>0</v>
@@ -2838,27 +2830,27 @@
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-33266</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
+          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t>MAIRIE DE CAPBRETON</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>Migracier activité Placier vers Geodp V2</t>
+          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
@@ -2873,12 +2865,12 @@
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I30" s="14" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J30" s="14" t="n">
@@ -2889,16 +2881,16 @@
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33245</t>
+          <t>PDMDEP-33272</t>
         </is>
       </c>
       <c r="M30" s="14" t="inlineStr">
         <is>
-          <t>00166748</t>
+          <t>00166910</t>
         </is>
       </c>
       <c r="N30" s="15" t="n">
-        <v>149</v>
+        <v>500</v>
       </c>
       <c r="O30" s="16" t="n">
         <v>0</v>
@@ -2910,32 +2902,32 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G31" s="11" t="inlineStr">
@@ -2945,12 +2937,12 @@
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J31" s="11" t="n">
@@ -2961,16 +2953,16 @@
       </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33232</t>
+          <t>PDMDEP-33245</t>
         </is>
       </c>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>00166708</t>
+          <t>00166748</t>
         </is>
       </c>
       <c r="N31" s="12" t="n">
-        <v>625</v>
+        <v>149</v>
       </c>
       <c r="O31" s="16" t="n">
         <v>0</v>
@@ -2982,32 +2974,32 @@
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33170</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr">
         <is>
-          <t>Commune de Bonneville</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F32" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G32" s="14" t="inlineStr">
@@ -3017,12 +3009,12 @@
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I32" s="14" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J32" s="14" t="n">
@@ -3033,16 +3025,16 @@
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33177</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M32" s="14" t="inlineStr">
         <is>
-          <t>00166356</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N32" s="15" t="n">
-        <v>910</v>
+        <v>625</v>
       </c>
       <c r="O32" s="16" t="n">
         <v>0</v>
@@ -3054,12 +3046,12 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33064</t>
+          <t>PDMDEP-33170</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
@@ -3069,12 +3061,12 @@
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LONGWY</t>
+          <t>Commune de Bonneville</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
@@ -3094,27 +3086,27 @@
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J33" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33073</t>
+          <t>PDMDEP-33177</t>
         </is>
       </c>
       <c r="M33" s="11" t="inlineStr">
         <is>
-          <t>00165708</t>
+          <t>00166356</t>
         </is>
       </c>
       <c r="N33" s="12" t="n">
-        <v>1207</v>
+        <v>910</v>
       </c>
       <c r="O33" s="16" t="n">
         <v>0</v>
@@ -3126,32 +3118,32 @@
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-33064</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>MAIRIE DE LONGWY</t>
         </is>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F34" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G34" s="14" t="inlineStr">
@@ -3161,32 +3153,32 @@
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="J34" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K34" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-33073</t>
         </is>
       </c>
       <c r="M34" s="14" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00165708</t>
         </is>
       </c>
       <c r="N34" s="15" t="n">
-        <v>500</v>
+        <v>1207</v>
       </c>
       <c r="O34" s="16" t="n">
         <v>0</v>
@@ -3198,27 +3190,27 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32768</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE REIMS</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>MV app/ infra + màj carto</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
@@ -3238,29 +3230,29 @@
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J35" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L35" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32772</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M35" s="11" t="inlineStr">
         <is>
-          <t>00163806</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" s="12" t="n">
+        <v>500</v>
+      </c>
+      <c r="O35" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P35" s="12" t="n">
@@ -3270,12 +3262,12 @@
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32768</t>
         </is>
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
@@ -3285,12 +3277,12 @@
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>VILLE DE REIMS</t>
         </is>
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="F36" s="14" t="inlineStr">
@@ -3310,29 +3302,29 @@
       </c>
       <c r="I36" s="14" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J36" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K36" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32556</t>
+          <t>PDMDEP-32772</t>
         </is>
       </c>
       <c r="M36" s="14" t="inlineStr">
         <is>
-          <t>00162313</t>
+          <t>00163806</t>
         </is>
       </c>
       <c r="N36" s="15" t="n">
-        <v>142.1</v>
-      </c>
-      <c r="O36" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P36" s="15" t="n">
@@ -3342,32 +3334,32 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G37" s="11" t="inlineStr">
@@ -3377,32 +3369,32 @@
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J37" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K37" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M37" s="11" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N37" s="12" t="n">
-        <v>2335</v>
+        <v>142.1</v>
       </c>
       <c r="O37" s="16" t="n">
         <v>0</v>
@@ -3414,27 +3406,27 @@
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D38" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F38" s="14" t="inlineStr">
@@ -3454,7 +3446,7 @@
       </c>
       <c r="I38" s="14" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J38" s="14" t="n">
@@ -3465,16 +3457,16 @@
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M38" s="14" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N38" s="15" t="n">
-        <v>450</v>
+        <v>2335</v>
       </c>
       <c r="O38" s="16" t="n">
         <v>0</v>
@@ -3486,12 +3478,12 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32442</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t>[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod  (03/26)</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
@@ -3501,12 +3493,12 @@
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE CHAMBERY</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
@@ -3526,29 +3518,29 @@
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="J39" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32446</t>
         </is>
       </c>
       <c r="M39" s="11" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161842</t>
         </is>
       </c>
       <c r="N39" s="12" t="n">
-        <v>910</v>
-      </c>
-      <c r="O39" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P39" s="12" t="n">
@@ -3558,12 +3550,12 @@
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
@@ -3573,12 +3565,12 @@
       </c>
       <c r="D40" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F40" s="14" t="inlineStr">
@@ -3593,12 +3585,12 @@
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I40" s="14" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J40" s="14" t="n">
@@ -3609,16 +3601,16 @@
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M40" s="14" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N40" s="15" t="n">
-        <v>590.15</v>
+        <v>450</v>
       </c>
       <c r="O40" s="16" t="n">
         <v>0</v>
@@ -3630,32 +3622,32 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G41" s="11" t="inlineStr">
@@ -3670,27 +3662,27 @@
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J41" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L41" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N41" s="12" t="n">
-        <v>285</v>
+        <v>910</v>
       </c>
       <c r="O41" s="16" t="n">
         <v>0</v>
@@ -3702,32 +3694,32 @@
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31967</t>
+          <t>PDMDEP-32086</t>
         </is>
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
         </is>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t>Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
@@ -3737,12 +3729,12 @@
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I42" s="14" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="J42" s="14" t="n">
@@ -3753,16 +3745,16 @@
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31971</t>
+          <t>PDMDEP-32095</t>
         </is>
       </c>
       <c r="M42" s="14" t="inlineStr">
         <is>
-          <t>00159863</t>
+          <t>00160474</t>
         </is>
       </c>
       <c r="N42" s="15" t="n">
-        <v>1325</v>
+        <v>590.15</v>
       </c>
       <c r="O42" s="16" t="n">
         <v>0</v>
@@ -3774,32 +3766,32 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G43" s="11" t="inlineStr">
@@ -3814,7 +3806,7 @@
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J43" s="11" t="n">
@@ -3825,16 +3817,16 @@
       </c>
       <c r="L43" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M43" s="11" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N43" s="12" t="n">
-        <v>120</v>
+        <v>285</v>
       </c>
       <c r="O43" s="16" t="n">
         <v>0</v>
@@ -3846,32 +3838,32 @@
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31908</t>
+          <t>PDMDEP-31967</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr">
         <is>
-          <t>Commune de GUINGAMP</t>
+          <t>DEPARTEMENT DU LOT -CD46</t>
         </is>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
@@ -3881,32 +3873,32 @@
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I44" s="14" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="J44" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K44" s="14" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31917</t>
+          <t>PDMDEP-31971</t>
         </is>
       </c>
       <c r="M44" s="14" t="inlineStr">
         <is>
-          <t>00159608</t>
+          <t>00159863</t>
         </is>
       </c>
       <c r="N44" s="15" t="n">
-        <v>588</v>
+        <v>1325</v>
       </c>
       <c r="O44" s="16" t="n">
         <v>0</v>
@@ -3918,32 +3910,32 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G45" s="11" t="inlineStr">
@@ -3953,32 +3945,32 @@
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J45" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K45" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N45" s="12" t="n">
-        <v>203.5</v>
+        <v>120</v>
       </c>
       <c r="O45" s="16" t="n">
         <v>0</v>
@@ -3990,27 +3982,27 @@
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-31908</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>Commune de GUINGAMP</t>
         </is>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
@@ -4030,27 +4022,27 @@
       </c>
       <c r="I46" s="14" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J46" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K46" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31596</t>
+          <t>PDMDEP-31917</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
         <is>
-          <t>00157967</t>
+          <t>00159608</t>
         </is>
       </c>
       <c r="N46" s="15" t="n">
-        <v>300</v>
+        <v>588</v>
       </c>
       <c r="O46" s="16" t="n">
         <v>0</v>
@@ -4062,32 +4054,32 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G47" s="11" t="inlineStr">
@@ -4097,12 +4089,12 @@
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J47" s="11" t="n">
@@ -4113,16 +4105,16 @@
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N47" s="12" t="n">
-        <v>700</v>
+        <v>203.5</v>
       </c>
       <c r="O47" s="16" t="n">
         <v>0</v>
@@ -4134,27 +4126,27 @@
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31589</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D48" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="F48" s="14" t="inlineStr">
@@ -4174,7 +4166,7 @@
       </c>
       <c r="I48" s="14" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J48" s="14" t="n">
@@ -4185,16 +4177,16 @@
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31596</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00157967</t>
         </is>
       </c>
       <c r="N48" s="15" t="n">
-        <v>210</v>
+        <v>300</v>
       </c>
       <c r="O48" s="16" t="n">
         <v>0</v>
@@ -4206,32 +4198,32 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G49" s="11" t="inlineStr">
@@ -4241,12 +4233,12 @@
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J49" s="11" t="n">
@@ -4257,16 +4249,16 @@
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31546</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00157816</t>
         </is>
       </c>
       <c r="N49" s="12" t="n">
-        <v>130</v>
+        <v>700</v>
       </c>
       <c r="O49" s="16" t="n">
         <v>0</v>
@@ -4278,12 +4270,12 @@
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
@@ -4293,12 +4285,12 @@
       </c>
       <c r="D50" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F50" s="14" t="inlineStr">
@@ -4318,7 +4310,7 @@
       </c>
       <c r="I50" s="14" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J50" s="14" t="n">
@@ -4329,16 +4321,16 @@
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M50" s="14" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N50" s="15" t="n">
-        <v>255</v>
+        <v>210</v>
       </c>
       <c r="O50" s="16" t="n">
         <v>0</v>
@@ -4350,12 +4342,12 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
@@ -4365,7 +4357,7 @@
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
@@ -4390,27 +4382,27 @@
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J51" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K51" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N51" s="12" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="O51" s="16" t="n">
         <v>0</v>
@@ -4422,32 +4414,32 @@
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D52" s="14" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
@@ -4457,32 +4449,32 @@
       </c>
       <c r="H52" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I52" s="14" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J52" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K52" s="14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L52" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M52" s="14" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N52" s="15" t="n">
-        <v>690</v>
+        <v>255</v>
       </c>
       <c r="O52" s="16" t="n">
         <v>0</v>
@@ -4494,32 +4486,32 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G53" s="11" t="inlineStr">
@@ -4529,12 +4521,12 @@
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J53" s="11" t="n">
@@ -4545,16 +4537,16 @@
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N53" s="12" t="n">
-        <v>187.5</v>
+        <v>140</v>
       </c>
       <c r="O53" s="16" t="n">
         <v>0</v>
@@ -4566,27 +4558,27 @@
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F54" s="14" t="inlineStr">
@@ -4606,27 +4598,27 @@
       </c>
       <c r="I54" s="14" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J54" s="14" t="n">
         <v>8</v>
       </c>
       <c r="K54" s="14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L54" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M54" s="14" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N54" s="15" t="n">
-        <v>787.5</v>
+        <v>690</v>
       </c>
       <c r="O54" s="16" t="n">
         <v>0</v>
@@ -4638,32 +4630,32 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>Migration V2</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G55" s="11" t="inlineStr">
@@ -4673,35 +4665,35 @@
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J55" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K55" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M55" s="11" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" s="12" t="n">
-        <v>362.5</v>
+        <v>187.5</v>
+      </c>
+      <c r="O55" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P55" s="12" t="n">
         <v>0</v>
@@ -4710,27 +4702,27 @@
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D56" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F56" s="14" t="inlineStr">
@@ -4745,32 +4737,32 @@
       </c>
       <c r="H56" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I56" s="14" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J56" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K56" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L56" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M56" s="14" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N56" s="15" t="n">
-        <v>1320</v>
+        <v>787.5</v>
       </c>
       <c r="O56" s="16" t="n">
         <v>0</v>
@@ -4782,54 +4774,70 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-26831</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>CD74</t>
+          <t>Commune de CLAMART</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>MAJ carto</t>
-        </is>
-      </c>
-      <c r="F57" s="11" t="inlineStr"/>
+          <t>Migration V2</t>
+        </is>
+      </c>
+      <c r="F57" s="11" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
       <c r="G57" s="11" t="inlineStr">
         <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="H57" s="11" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H57" s="11" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J57" s="11" t="n">
         <v>10</v>
       </c>
       <c r="K57" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L57" s="11" t="inlineStr"/>
-      <c r="M57" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L57" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28310</t>
+        </is>
+      </c>
+      <c r="M57" s="11" t="inlineStr">
+        <is>
+          <t>00145374</t>
+        </is>
+      </c>
       <c r="N57" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O57" s="12" t="n">
-        <v>0</v>
+        <v>362.5</v>
       </c>
       <c r="P57" s="12" t="n">
         <v>0</v>
@@ -4838,12 +4846,12 @@
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
@@ -4853,11 +4861,13 @@
       </c>
       <c r="D58" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
-        </is>
-      </c>
-      <c r="E58" s="14" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E58" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F58" s="14" t="inlineStr">
         <is>
@@ -4876,29 +4886,29 @@
       </c>
       <c r="I58" s="14" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J58" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K58" s="14" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="L58" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M58" s="14" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N58" s="15" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O58" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P58" s="15" t="n">
@@ -4908,12 +4918,12 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
@@ -4923,11 +4933,13 @@
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
-        </is>
-      </c>
-      <c r="E59" s="11" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E59" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
         <is>
@@ -4946,23 +4958,23 @@
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J59" s="11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K59" s="11" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="L59" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M59" s="11" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N59" s="12" t="n">
@@ -4978,26 +4990,28 @@
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D60" s="14" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
-        </is>
-      </c>
-      <c r="E60" s="14" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E60" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F60" s="14" t="inlineStr">
         <is>
@@ -5011,34 +5025,34 @@
       </c>
       <c r="H60" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I60" s="14" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J60" s="14" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K60" s="14" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="L60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M60" s="14" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N60" s="15" t="n">
-        <v>401</v>
-      </c>
-      <c r="O60" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P60" s="15" t="n">
@@ -5048,26 +5062,28 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
-        </is>
-      </c>
-      <c r="E61" s="11" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E61" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
@@ -5086,23 +5102,23 @@
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J61" s="11" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>1.25</v>
+        <v>0.3</v>
       </c>
       <c r="L61" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M61" s="11" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N61" s="12" t="n">
@@ -5118,26 +5134,28 @@
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C62" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D62" s="14" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
-        </is>
-      </c>
-      <c r="E62" s="14" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E62" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F62" s="14" t="inlineStr">
         <is>
@@ -5151,32 +5169,32 @@
       </c>
       <c r="H62" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I62" s="14" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J62" s="14" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="K62" s="14" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="L62" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M62" s="14" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N62" s="15" t="n">
-        <v>230</v>
+        <v>1320</v>
       </c>
       <c r="O62" s="16" t="n">
         <v>0</v>
@@ -5188,22 +5206,22 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-27634</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
         </is>
       </c>
       <c r="E63" s="11" t="n">
@@ -5216,27 +5234,35 @@
       </c>
       <c r="G63" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="J63" s="11" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="K63" s="11" t="n">
         <v>0.5</v>
       </c>
-      <c r="L63" s="11" t="inlineStr"/>
-      <c r="M63" s="11" t="inlineStr"/>
+      <c r="L63" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27642</t>
+        </is>
+      </c>
+      <c r="M63" s="11" t="inlineStr">
+        <is>
+          <t>00143935</t>
+        </is>
+      </c>
       <c r="N63" s="12" t="n">
         <v>0</v>
       </c>
@@ -5250,67 +5276,53 @@
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-26831</t>
         </is>
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D64" s="14" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
-        </is>
-      </c>
-      <c r="E64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="F64" s="14" t="inlineStr">
-        <is>
-          <t>GEODP</t>
-        </is>
-      </c>
+          <t>CD74</t>
+        </is>
+      </c>
+      <c r="E64" s="14" t="inlineStr">
+        <is>
+          <t>MAJ carto</t>
+        </is>
+      </c>
+      <c r="F64" s="14" t="inlineStr"/>
       <c r="G64" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H64" s="14" t="inlineStr">
-        <is>
-          <t>Migration</t>
-        </is>
-      </c>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="H64" s="14" t="inlineStr"/>
       <c r="I64" s="14" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="J64" s="14" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="K64" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M64" s="14" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L64" s="14" t="inlineStr"/>
+      <c r="M64" s="14" t="inlineStr"/>
       <c r="N64" s="15" t="n">
-        <v>240</v>
-      </c>
-      <c r="O64" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P64" s="15" t="n">
@@ -5320,22 +5332,22 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-26813</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>VILLE DE VILLEJUIF</t>
         </is>
       </c>
       <c r="E65" s="11" t="n">
@@ -5358,29 +5370,29 @@
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J65" s="11" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="K65" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28023</t>
+          <t>PDMDEP-26814</t>
         </is>
       </c>
       <c r="M65" s="11" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>00142941</t>
         </is>
       </c>
       <c r="N65" s="12" t="n">
-        <v>557.145</v>
-      </c>
-      <c r="O65" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P65" s="12" t="n">
@@ -5390,12 +5402,12 @@
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-13128</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>[VALENCIENNES] Littéralis Prime - RAF FAST PARAPHEUR - Déjà facturé</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C66" s="14" t="inlineStr">
@@ -5405,7 +5417,7 @@
       </c>
       <c r="D66" s="14" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
         </is>
       </c>
       <c r="E66" s="14" t="n">
@@ -5418,7 +5430,7 @@
       </c>
       <c r="G66" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H66" s="14" t="inlineStr">
@@ -5428,21 +5440,29 @@
       </c>
       <c r="I66" s="14" t="inlineStr">
         <is>
-          <t>30/10/2023</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J66" s="14" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="K66" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L66" s="14" t="inlineStr"/>
-      <c r="M66" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L66" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27017</t>
+        </is>
+      </c>
+      <c r="M66" s="14" t="inlineStr">
+        <is>
+          <t>00141205</t>
+        </is>
+      </c>
       <c r="N66" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O66" s="15" t="n">
+        <v>1212</v>
+      </c>
+      <c r="O66" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P66" s="15" t="n">
@@ -5452,22 +5472,22 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E67" s="11" t="n">
@@ -5485,28 +5505,28 @@
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J67" s="11" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27990</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
-          <t>406296</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N67" s="12" t="n">
@@ -5522,22 +5542,22 @@
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C68" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D68" s="14" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E68" s="14" t="n">
@@ -5550,27 +5570,39 @@
       </c>
       <c r="G68" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H68" s="14" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H68" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I68" s="14" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J68" s="14" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="K68" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L68" s="14" t="inlineStr"/>
-      <c r="M68" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L68" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27373</t>
+        </is>
+      </c>
+      <c r="M68" s="14" t="inlineStr">
+        <is>
+          <t>466234</t>
+        </is>
+      </c>
       <c r="N68" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O68" s="15" t="n">
+        <v>401</v>
+      </c>
+      <c r="O68" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P68" s="15" t="n">
@@ -5580,89 +5612,683 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
+          <t>PDMDEP-21222</t>
+        </is>
+      </c>
+      <c r="B69" s="11" t="inlineStr">
+        <is>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
+        </is>
+      </c>
+      <c r="C69" s="11" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D69" s="11" t="inlineStr">
+        <is>
+          <t>ISSY LES MOULINEAUX</t>
+        </is>
+      </c>
+      <c r="E69" s="11" t="n">
+        <v/>
+      </c>
+      <c r="F69" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G69" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H69" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I69" s="11" t="inlineStr">
+        <is>
+          <t>23/04/2025</t>
+        </is>
+      </c>
+      <c r="J69" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="K69" s="11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L69" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28036</t>
+        </is>
+      </c>
+      <c r="M69" s="11" t="inlineStr">
+        <is>
+          <t>483799</t>
+        </is>
+      </c>
+      <c r="N69" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-20907</t>
+        </is>
+      </c>
+      <c r="B70" s="14" t="inlineStr">
+        <is>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="C70" s="14" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D70" s="14" t="inlineStr">
+        <is>
+          <t>SAINT PIERRE (LA REUNION)</t>
+        </is>
+      </c>
+      <c r="E70" s="14" t="n">
+        <v/>
+      </c>
+      <c r="F70" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G70" s="14" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H70" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I70" s="14" t="inlineStr">
+        <is>
+          <t>14/04/2025</t>
+        </is>
+      </c>
+      <c r="J70" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="K70" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28034</t>
+        </is>
+      </c>
+      <c r="M70" s="14" t="inlineStr">
+        <is>
+          <t>475575</t>
+        </is>
+      </c>
+      <c r="N70" s="15" t="n">
+        <v>230</v>
+      </c>
+      <c r="O70" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-18241</t>
+        </is>
+      </c>
+      <c r="B71" s="11" t="inlineStr">
+        <is>
+          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
+        </is>
+      </c>
+      <c r="C71" s="11" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="D71" s="11" t="inlineStr">
+        <is>
+          <t>CD 74 - HAUTE SAVOIE</t>
+        </is>
+      </c>
+      <c r="E71" s="11" t="n">
+        <v/>
+      </c>
+      <c r="F71" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G71" s="11" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H71" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I71" s="11" t="inlineStr">
+        <is>
+          <t>20/12/2024</t>
+        </is>
+      </c>
+      <c r="J71" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="K71" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L71" s="11" t="inlineStr"/>
+      <c r="M71" s="11" t="inlineStr"/>
+      <c r="N71" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-18240</t>
+        </is>
+      </c>
+      <c r="B72" s="14" t="inlineStr">
+        <is>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+        </is>
+      </c>
+      <c r="C72" s="14" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D72" s="14" t="inlineStr">
+        <is>
+          <t>Biarritz</t>
+        </is>
+      </c>
+      <c r="E72" s="14" t="n">
+        <v/>
+      </c>
+      <c r="F72" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G72" s="14" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H72" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I72" s="14" t="inlineStr">
+        <is>
+          <t>20/12/2024</t>
+        </is>
+      </c>
+      <c r="J72" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="K72" s="14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L72" s="14" t="inlineStr"/>
+      <c r="M72" s="14" t="inlineStr"/>
+      <c r="N72" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-18115</t>
+        </is>
+      </c>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
+        </is>
+      </c>
+      <c r="C73" s="11" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="D73" s="11" t="inlineStr">
+        <is>
+          <t>BISCHWILLER</t>
+        </is>
+      </c>
+      <c r="E73" s="11" t="n">
+        <v/>
+      </c>
+      <c r="F73" s="11" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="G73" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H73" s="11" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="I73" s="11" t="inlineStr">
+        <is>
+          <t>17/12/2024</t>
+        </is>
+      </c>
+      <c r="J73" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="K73" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28019</t>
+        </is>
+      </c>
+      <c r="M73" s="11" t="inlineStr">
+        <is>
+          <t>455151</t>
+        </is>
+      </c>
+      <c r="N73" s="12" t="n">
+        <v>240</v>
+      </c>
+      <c r="O73" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-18037</t>
+        </is>
+      </c>
+      <c r="B74" s="14" t="inlineStr">
+        <is>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+        </is>
+      </c>
+      <c r="C74" s="14" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D74" s="14" t="inlineStr">
+        <is>
+          <t>LE PERREUX SUR MARNE</t>
+        </is>
+      </c>
+      <c r="E74" s="14" t="n">
+        <v/>
+      </c>
+      <c r="F74" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G74" s="14" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H74" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I74" s="14" t="inlineStr">
+        <is>
+          <t>12/12/2024</t>
+        </is>
+      </c>
+      <c r="J74" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="K74" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M74" s="14" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
+      <c r="N74" s="15" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O74" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-13128</t>
+        </is>
+      </c>
+      <c r="B75" s="11" t="inlineStr">
+        <is>
+          <t>[VALENCIENNES] Littéralis Prime - RAF FAST PARAPHEUR - Déjà facturé</t>
+        </is>
+      </c>
+      <c r="C75" s="11" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="D75" s="11" t="inlineStr">
+        <is>
+          <t>Valenciennes</t>
+        </is>
+      </c>
+      <c r="E75" s="11" t="n">
+        <v/>
+      </c>
+      <c r="F75" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G75" s="11" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H75" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I75" s="11" t="inlineStr">
+        <is>
+          <t>30/10/2023</t>
+        </is>
+      </c>
+      <c r="J75" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="K75" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L75" s="11" t="inlineStr"/>
+      <c r="M75" s="11" t="inlineStr"/>
+      <c r="N75" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-12747</t>
+        </is>
+      </c>
+      <c r="B76" s="14" t="inlineStr">
+        <is>
+          <t>[FOUGERES] ARPEGE</t>
+        </is>
+      </c>
+      <c r="C76" s="14" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D76" s="14" t="inlineStr">
+        <is>
+          <t>FOUGERES</t>
+        </is>
+      </c>
+      <c r="E76" s="14" t="n">
+        <v/>
+      </c>
+      <c r="F76" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G76" s="14" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H76" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I76" s="14" t="inlineStr">
+        <is>
+          <t>26/09/2023</t>
+        </is>
+      </c>
+      <c r="J76" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="K76" s="14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L76" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M76" s="14" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
+      <c r="N76" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-12708</t>
+        </is>
+      </c>
+      <c r="B77" s="11" t="inlineStr">
+        <is>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C77" s="11" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="D77" s="11" t="inlineStr">
+        <is>
+          <t>CD 56 MORBIHAN</t>
+        </is>
+      </c>
+      <c r="E77" s="11" t="n">
+        <v/>
+      </c>
+      <c r="F77" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G77" s="11" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H77" s="11" t="inlineStr"/>
+      <c r="I77" s="11" t="inlineStr">
+        <is>
+          <t>22/09/2023</t>
+        </is>
+      </c>
+      <c r="J77" s="11" t="n">
+        <v>36</v>
+      </c>
+      <c r="K77" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L77" s="11" t="inlineStr"/>
+      <c r="M77" s="11" t="inlineStr"/>
+      <c r="N77" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="13" t="inlineStr">
+        <is>
           <t>PDMDEP-11477</t>
         </is>
       </c>
-      <c r="B69" s="11" t="inlineStr">
+      <c r="B78" s="14" t="inlineStr">
         <is>
           <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
-      <c r="C69" s="11" t="inlineStr"/>
-      <c r="D69" s="11" t="inlineStr">
+      <c r="C78" s="14" t="inlineStr"/>
+      <c r="D78" s="14" t="inlineStr">
         <is>
           <t>MONTPELLIER MMM</t>
         </is>
       </c>
-      <c r="E69" s="11" t="inlineStr">
+      <c r="E78" s="14" t="inlineStr">
         <is>
           <t>Déploiement Module AC</t>
         </is>
       </c>
-      <c r="F69" s="11" t="inlineStr">
+      <c r="F78" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="G69" s="11" t="inlineStr">
+      <c r="G78" s="14" t="inlineStr">
         <is>
           <t>Rework</t>
         </is>
       </c>
-      <c r="H69" s="11" t="inlineStr">
+      <c r="H78" s="14" t="inlineStr">
         <is>
           <t>Nouveau déploiement</t>
         </is>
       </c>
-      <c r="I69" s="11" t="inlineStr">
+      <c r="I78" s="14" t="inlineStr">
         <is>
           <t>03/09/2023</t>
         </is>
       </c>
-      <c r="J69" s="11" t="n">
+      <c r="J78" s="14" t="n">
         <v>36</v>
       </c>
-      <c r="K69" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L69" s="11" t="inlineStr"/>
-      <c r="M69" s="11" t="inlineStr"/>
-      <c r="N69" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O69" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P69" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="17" t="inlineStr">
+      <c r="K78" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L78" s="14" t="inlineStr"/>
+      <c r="M78" s="14" t="inlineStr"/>
+      <c r="N78" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B70" s="17" t="inlineStr"/>
-      <c r="C70" s="17" t="inlineStr"/>
-      <c r="D70" s="17" t="inlineStr"/>
-      <c r="E70" s="17" t="inlineStr"/>
-      <c r="F70" s="17" t="inlineStr"/>
-      <c r="G70" s="17" t="inlineStr"/>
-      <c r="H70" s="17" t="inlineStr"/>
-      <c r="I70" s="17" t="inlineStr"/>
-      <c r="J70" s="17" t="inlineStr"/>
-      <c r="K70" s="17" t="inlineStr"/>
-      <c r="L70" s="17" t="inlineStr"/>
-      <c r="M70" s="17" t="inlineStr"/>
-      <c r="N70" s="18" t="n">
+      <c r="B79" s="17" t="inlineStr"/>
+      <c r="C79" s="17" t="inlineStr"/>
+      <c r="D79" s="17" t="inlineStr"/>
+      <c r="E79" s="17" t="inlineStr"/>
+      <c r="F79" s="17" t="inlineStr"/>
+      <c r="G79" s="17" t="inlineStr"/>
+      <c r="H79" s="17" t="inlineStr"/>
+      <c r="I79" s="17" t="inlineStr"/>
+      <c r="J79" s="17" t="inlineStr"/>
+      <c r="K79" s="17" t="inlineStr"/>
+      <c r="L79" s="17" t="inlineStr"/>
+      <c r="M79" s="17" t="inlineStr"/>
+      <c r="N79" s="18" t="n">
         <v>47526.995</v>
       </c>
-      <c r="O70" s="18" t="n">
-        <v>362.5</v>
-      </c>
-      <c r="P70" s="18" t="n">
-        <v>16.67</v>
+      <c r="O79" s="18" t="n">
+        <v>1265.22</v>
+      </c>
+      <c r="P79" s="18" t="n">
+        <v>40.81</v>
       </c>
     </row>
   </sheetData>
@@ -5733,6 +6359,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId63"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A73" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A74" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A75" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId74"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6307,16 +6942,16 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>11</v>
+        <v>15.25</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>2.25</v>
+        <v>4.75</v>
       </c>
       <c r="D5" s="14" t="n">
         <v>1.5</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>14.75</v>
+        <v>21.5</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>2.5</v>
@@ -6326,7 +6961,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
     </row>
@@ -6343,10 +6978,10 @@
         <v>0</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>2</v>
@@ -6356,7 +6991,7 @@
       </c>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>3.1%</t>
         </is>
       </c>
     </row>
@@ -6368,7 +7003,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>13</v>
+        <v>17.25</v>
       </c>
     </row>
   </sheetData>
@@ -6453,10 +7088,10 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>366023</v>
+        <v>365120</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>133933</v>
+        <v>133030</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>232090</v>
@@ -6478,10 +7113,10 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>164283</v>
+        <v>163380</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>60635</v>
+        <v>59733</v>
       </c>
       <c r="D6" s="25" t="n">
         <v>103647</v>
